--- a/プロジェクト型演習_成果物_TasBo_コメント投稿.xlsx
+++ b/プロジェクト型演習_成果物_TasBo_コメント投稿.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER111\Desktop\TasBoドキュメント\コメント投稿\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TasBo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96377BD1-D793-4162-A0FA-F5A2E1E29BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6DEB254-ACE8-457D-A9F5-D22DDD5820E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,6 @@
     <definedName name="範囲１">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="95">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -1543,7 +1542,7 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="193">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1685,20 +1684,341 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="6" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1718,221 +2038,59 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="6" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1940,188 +2098,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2250,6 +2234,360 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1062404</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>234462</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>989135</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>250847</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="直線コネクタ 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{622F1097-A57E-8EFD-6668-DE8401BDBA66}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2095500" y="3348404"/>
+          <a:ext cx="1040423" cy="16385"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="dash"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>952501</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>820616</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>131884</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>820616</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="直線コネクタ 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1872CFA5-9470-BE10-D0D5-E8499186304D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3099289" y="3934558"/>
+          <a:ext cx="293076" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="dash"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1099039</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>819150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>438151</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>819150</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="直線コネクタ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDFF7B3E-214D-65A1-3108-42B02E2F0833}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2132135" y="3933092"/>
+          <a:ext cx="452804" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="dash"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>879230</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>131885</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="256160" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="テキスト ボックス 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF526710-A181-4CDE-7BB5-3EDFF91FDF54}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1912326" y="3245827"/>
+          <a:ext cx="256160" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>1</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>108437</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>679939</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="256160" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="テキスト ボックス 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1FAA505-BA0E-40C2-BC92-BD1EA1DD801D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3368918" y="3793881"/>
+          <a:ext cx="256160" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>2</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>868972</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>685800</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="256160" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="テキスト ボックス 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA9BDB0A-56A2-4E67-8DA3-44486D2250F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1902068" y="3799742"/>
+          <a:ext cx="256160" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>3</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2460,85 +2798,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="94" t="s">
+      <c r="C2" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="95"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="114"/>
+      <c r="O2" s="114"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="93"/>
-      <c r="L3" s="93"/>
-      <c r="M3" s="93"/>
-      <c r="N3" s="93"/>
-      <c r="O3" s="93"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="87"/>
+      <c r="J3" s="87"/>
+      <c r="K3" s="87"/>
+      <c r="L3" s="87"/>
+      <c r="M3" s="87"/>
+      <c r="N3" s="87"/>
+      <c r="O3" s="87"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="93"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="93"/>
-      <c r="J4" s="93"/>
-      <c r="K4" s="93"/>
-      <c r="L4" s="93"/>
-      <c r="M4" s="93"/>
-      <c r="N4" s="93"/>
-      <c r="O4" s="93"/>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
+      <c r="M4" s="87"/>
+      <c r="N4" s="87"/>
+      <c r="O4" s="87"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="93"/>
-      <c r="D5" s="93"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
-      <c r="G5" s="93"/>
-      <c r="H5" s="93"/>
-      <c r="I5" s="93"/>
-      <c r="J5" s="93"/>
-      <c r="K5" s="93"/>
-      <c r="L5" s="93"/>
-      <c r="M5" s="93"/>
-      <c r="N5" s="93"/>
-      <c r="O5" s="93"/>
+      <c r="C5" s="87"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="87"/>
+      <c r="J5" s="87"/>
+      <c r="K5" s="87"/>
+      <c r="L5" s="87"/>
+      <c r="M5" s="87"/>
+      <c r="N5" s="87"/>
+      <c r="O5" s="87"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="93"/>
-      <c r="D6" s="93"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="93"/>
-      <c r="G6" s="93"/>
-      <c r="H6" s="93"/>
-      <c r="I6" s="93"/>
-      <c r="J6" s="93"/>
-      <c r="K6" s="93"/>
-      <c r="L6" s="93"/>
-      <c r="M6" s="93"/>
-      <c r="N6" s="93"/>
-      <c r="O6" s="93"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="87"/>
+      <c r="E6" s="87"/>
+      <c r="F6" s="87"/>
+      <c r="G6" s="87"/>
+      <c r="H6" s="87"/>
+      <c r="I6" s="87"/>
+      <c r="J6" s="87"/>
+      <c r="K6" s="87"/>
+      <c r="L6" s="87"/>
+      <c r="M6" s="87"/>
+      <c r="N6" s="87"/>
+      <c r="O6" s="87"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2558,46 +2896,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="96" t="s">
+      <c r="E8" s="115" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="93"/>
-      <c r="G8" s="93"/>
-      <c r="H8" s="93"/>
-      <c r="I8" s="93"/>
-      <c r="J8" s="93"/>
-      <c r="K8" s="93"/>
-      <c r="L8" s="93"/>
-      <c r="M8" s="93"/>
+      <c r="F8" s="87"/>
+      <c r="G8" s="87"/>
+      <c r="H8" s="87"/>
+      <c r="I8" s="87"/>
+      <c r="J8" s="87"/>
+      <c r="K8" s="87"/>
+      <c r="L8" s="87"/>
+      <c r="M8" s="87"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="89" t="s">
+      <c r="G13" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="91"/>
-      <c r="I13" s="97">
+      <c r="H13" s="69"/>
+      <c r="I13" s="116">
         <v>46196</v>
       </c>
-      <c r="J13" s="90"/>
-      <c r="K13" s="91"/>
+      <c r="J13" s="54"/>
+      <c r="K13" s="69"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="89"/>
-      <c r="H14" s="91"/>
-      <c r="I14" s="97"/>
-      <c r="J14" s="90"/>
-      <c r="K14" s="91"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="116"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="69"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="89"/>
-      <c r="H15" s="91"/>
-      <c r="I15" s="89"/>
-      <c r="J15" s="90"/>
-      <c r="K15" s="91"/>
+      <c r="G15" s="111"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="111"/>
+      <c r="J15" s="54"/>
+      <c r="K15" s="69"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2606,13 +2944,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="92" t="s">
+      <c r="G17" s="112" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="93"/>
-      <c r="I17" s="93"/>
-      <c r="J17" s="93"/>
-      <c r="K17" s="93"/>
+      <c r="H17" s="87"/>
+      <c r="I17" s="87"/>
+      <c r="J17" s="87"/>
+      <c r="K17" s="87"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3626,19 +3964,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="112" t="s">
+      <c r="B1" s="100"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="113"/>
-      <c r="F1" s="112" t="s">
+      <c r="E1" s="78"/>
+      <c r="F1" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="113"/>
+      <c r="G1" s="78"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -3650,40 +3988,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="107"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="101"/>
+      <c r="A2" s="102"/>
+      <c r="B2" s="87"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="97"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="107"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="108"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="108"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="102"/>
+      <c r="A3" s="102"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="98"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="109"/>
-      <c r="B4" s="110"/>
-      <c r="C4" s="111"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="111"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="103"/>
+      <c r="A4" s="119"/>
+      <c r="B4" s="120"/>
+      <c r="C4" s="121"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -5040,19 +5378,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="139" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="83" t="s">
+      <c r="B1" s="140"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="148" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="71"/>
-      <c r="F1" s="83" t="s">
+      <c r="E1" s="131"/>
+      <c r="F1" s="148" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="71"/>
+      <c r="G1" s="131"/>
       <c r="H1" s="44" t="s">
         <v>5</v>
       </c>
@@ -5064,194 +5402,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="77"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="84" t="s">
+      <c r="A2" s="142"/>
+      <c r="B2" s="143"/>
+      <c r="C2" s="144"/>
+      <c r="D2" s="149" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="85"/>
-      <c r="F2" s="84" t="s">
+      <c r="E2" s="150"/>
+      <c r="F2" s="149" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="85"/>
-      <c r="H2" s="88">
+      <c r="G2" s="150"/>
+      <c r="H2" s="153">
         <v>46195</v>
       </c>
-      <c r="I2" s="63" t="s">
+      <c r="I2" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="66"/>
+      <c r="J2" s="126"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="77"/>
-      <c r="B3" s="78"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="67"/>
+      <c r="A3" s="142"/>
+      <c r="B3" s="143"/>
+      <c r="C3" s="144"/>
+      <c r="D3" s="151"/>
+      <c r="E3" s="144"/>
+      <c r="F3" s="151"/>
+      <c r="G3" s="144"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="127"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="80"/>
-      <c r="B4" s="81"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="87"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="68"/>
+      <c r="A4" s="145"/>
+      <c r="B4" s="146"/>
+      <c r="C4" s="147"/>
+      <c r="D4" s="152"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="152"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="128"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="129" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="72" t="s">
+      <c r="B5" s="130"/>
+      <c r="C5" s="131"/>
+      <c r="D5" s="132" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="73"/>
+      <c r="E5" s="130"/>
+      <c r="F5" s="130"/>
+      <c r="G5" s="130"/>
+      <c r="H5" s="130"/>
+      <c r="I5" s="130"/>
+      <c r="J5" s="133"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="58" t="s">
+      <c r="B6" s="135"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="137" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="49"/>
+      <c r="E6" s="135"/>
+      <c r="F6" s="135"/>
+      <c r="G6" s="135"/>
+      <c r="H6" s="135"/>
+      <c r="I6" s="135"/>
+      <c r="J6" s="138"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="134" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="58" t="s">
+      <c r="B7" s="135"/>
+      <c r="C7" s="136"/>
+      <c r="D7" s="137" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="49"/>
+      <c r="E7" s="135"/>
+      <c r="F7" s="135"/>
+      <c r="G7" s="135"/>
+      <c r="H7" s="135"/>
+      <c r="I7" s="135"/>
+      <c r="J7" s="138"/>
     </row>
     <row r="8" spans="1:10" ht="56.25" customHeight="1">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="134" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="47" t="s">
+      <c r="B8" s="135"/>
+      <c r="C8" s="136"/>
+      <c r="D8" s="154" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="49"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="135"/>
+      <c r="G8" s="135"/>
+      <c r="H8" s="135"/>
+      <c r="I8" s="135"/>
+      <c r="J8" s="138"/>
     </row>
     <row r="9" spans="1:10" ht="147.75" customHeight="1">
-      <c r="A9" s="59" t="s">
+      <c r="A9" s="155" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="62" t="s">
+      <c r="B9" s="158" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="51"/>
-      <c r="D9" s="47" t="s">
+      <c r="C9" s="136"/>
+      <c r="D9" s="154" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="49"/>
+      <c r="E9" s="135"/>
+      <c r="F9" s="135"/>
+      <c r="G9" s="135"/>
+      <c r="H9" s="135"/>
+      <c r="I9" s="135"/>
+      <c r="J9" s="138"/>
     </row>
     <row r="10" spans="1:10" ht="348" customHeight="1">
-      <c r="A10" s="60"/>
-      <c r="B10" s="62" t="s">
+      <c r="A10" s="156"/>
+      <c r="B10" s="158" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="51"/>
-      <c r="D10" s="47" t="s">
+      <c r="C10" s="136"/>
+      <c r="D10" s="154" t="s">
         <v>84</v>
       </c>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="49"/>
+      <c r="E10" s="135"/>
+      <c r="F10" s="135"/>
+      <c r="G10" s="135"/>
+      <c r="H10" s="135"/>
+      <c r="I10" s="135"/>
+      <c r="J10" s="138"/>
     </row>
     <row r="11" spans="1:10" ht="102.75" customHeight="1">
-      <c r="A11" s="61"/>
-      <c r="B11" s="62" t="s">
+      <c r="A11" s="157"/>
+      <c r="B11" s="158" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="47" t="s">
+      <c r="C11" s="136"/>
+      <c r="D11" s="154" t="s">
         <v>85</v>
       </c>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="49"/>
+      <c r="E11" s="135"/>
+      <c r="F11" s="135"/>
+      <c r="G11" s="135"/>
+      <c r="H11" s="135"/>
+      <c r="I11" s="135"/>
+      <c r="J11" s="138"/>
     </row>
     <row r="12" spans="1:10" ht="46.5" customHeight="1">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="134" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="48"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="47" t="s">
+      <c r="B12" s="135"/>
+      <c r="C12" s="136"/>
+      <c r="D12" s="154" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="48"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="49"/>
+      <c r="E12" s="135"/>
+      <c r="F12" s="135"/>
+      <c r="G12" s="135"/>
+      <c r="H12" s="135"/>
+      <c r="I12" s="135"/>
+      <c r="J12" s="138"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="52" t="s">
+      <c r="A13" s="159" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="53"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="55" t="s">
+      <c r="B13" s="160"/>
+      <c r="C13" s="161"/>
+      <c r="D13" s="162" t="s">
         <v>83</v>
       </c>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="56"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="56"/>
-      <c r="J13" s="57"/>
+      <c r="E13" s="163"/>
+      <c r="F13" s="163"/>
+      <c r="G13" s="163"/>
+      <c r="H13" s="163"/>
+      <c r="I13" s="163"/>
+      <c r="J13" s="164"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -6242,6 +6580,21 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A5:C5"/>
@@ -6254,21 +6607,6 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:J13"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -6288,19 +6626,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="165" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="83" t="s">
+      <c r="B1" s="140"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="148" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="71"/>
-      <c r="F1" s="83" t="s">
+      <c r="E1" s="131"/>
+      <c r="F1" s="148" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="71"/>
+      <c r="G1" s="131"/>
       <c r="H1" s="45" t="s">
         <v>5</v>
       </c>
@@ -6312,48 +6650,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="77"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="84" t="s">
+      <c r="A2" s="142"/>
+      <c r="B2" s="143"/>
+      <c r="C2" s="144"/>
+      <c r="D2" s="149" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="85"/>
-      <c r="F2" s="84" t="s">
+      <c r="E2" s="150"/>
+      <c r="F2" s="149" t="s">
         <v>74</v>
       </c>
-      <c r="G2" s="85"/>
-      <c r="H2" s="119">
+      <c r="G2" s="150"/>
+      <c r="H2" s="166">
         <v>46196</v>
       </c>
-      <c r="I2" s="63" t="s">
+      <c r="I2" s="123" t="s">
         <v>73</v>
       </c>
-      <c r="J2" s="66"/>
+      <c r="J2" s="126"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="77"/>
-      <c r="B3" s="78"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="67"/>
+      <c r="A3" s="142"/>
+      <c r="B3" s="143"/>
+      <c r="C3" s="144"/>
+      <c r="D3" s="151"/>
+      <c r="E3" s="144"/>
+      <c r="F3" s="151"/>
+      <c r="G3" s="144"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="127"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="80"/>
-      <c r="B4" s="81"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="87"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="68"/>
+      <c r="A4" s="145"/>
+      <c r="B4" s="146"/>
+      <c r="C4" s="147"/>
+      <c r="D4" s="152"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="152"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="128"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="42"/>
@@ -7802,19 +8140,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="99" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="112" t="s">
+      <c r="B1" s="100"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="113"/>
-      <c r="F1" s="112" t="s">
+      <c r="E1" s="78"/>
+      <c r="F1" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="113"/>
+      <c r="G1" s="78"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -7826,203 +8164,203 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="107"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="114" t="s">
+      <c r="A2" s="102"/>
+      <c r="B2" s="87"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="89" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="115"/>
-      <c r="F2" s="114" t="s">
+      <c r="E2" s="90"/>
+      <c r="F2" s="89" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="115"/>
-      <c r="H2" s="125">
+      <c r="G2" s="90"/>
+      <c r="H2" s="94">
         <v>46196</v>
       </c>
-      <c r="I2" s="98" t="s">
+      <c r="I2" s="96" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="101"/>
+      <c r="J2" s="97"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="107"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="108"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="116"/>
-      <c r="G3" s="108"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="102"/>
+      <c r="A3" s="102"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="98"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="107"/>
-      <c r="B4" s="93"/>
-      <c r="C4" s="108"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="108"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="102"/>
+      <c r="A4" s="102"/>
+      <c r="B4" s="87"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="92"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="92"/>
+      <c r="H4" s="95"/>
+      <c r="I4" s="95"/>
+      <c r="J4" s="98"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="165" t="s">
+      <c r="A5" s="74" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="166"/>
-      <c r="C5" s="167"/>
-      <c r="D5" s="168" t="s">
+      <c r="B5" s="75"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="81" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="166"/>
-      <c r="F5" s="166"/>
-      <c r="G5" s="166"/>
-      <c r="H5" s="166"/>
-      <c r="I5" s="166"/>
-      <c r="J5" s="169"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="82"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="170" t="s">
+      <c r="A6" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="90"/>
-      <c r="C6" s="90"/>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90"/>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
-      <c r="J6" s="171"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="55"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="172"/>
-      <c r="B7" s="129"/>
-      <c r="C7" s="129"/>
-      <c r="D7" s="129"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="129"/>
-      <c r="G7" s="129"/>
-      <c r="H7" s="129"/>
-      <c r="I7" s="129"/>
-      <c r="J7" s="173"/>
+      <c r="A7" s="83"/>
+      <c r="B7" s="84"/>
+      <c r="C7" s="84"/>
+      <c r="D7" s="84"/>
+      <c r="E7" s="84"/>
+      <c r="F7" s="84"/>
+      <c r="G7" s="84"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="84"/>
+      <c r="J7" s="85"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="174"/>
-      <c r="B8" s="175"/>
-      <c r="C8" s="175"/>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
-      <c r="F8" s="175"/>
-      <c r="G8" s="175"/>
-      <c r="H8" s="175"/>
-      <c r="I8" s="175"/>
-      <c r="J8" s="176"/>
+      <c r="A8" s="86"/>
+      <c r="B8" s="87"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="87"/>
+      <c r="E8" s="87"/>
+      <c r="F8" s="87"/>
+      <c r="G8" s="87"/>
+      <c r="H8" s="87"/>
+      <c r="I8" s="87"/>
+      <c r="J8" s="88"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="174"/>
-      <c r="B9" s="175"/>
-      <c r="C9" s="175"/>
-      <c r="D9" s="175"/>
-      <c r="E9" s="175"/>
-      <c r="F9" s="175"/>
-      <c r="G9" s="175"/>
-      <c r="H9" s="175"/>
-      <c r="I9" s="175"/>
-      <c r="J9" s="176"/>
+      <c r="A9" s="86"/>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
+      <c r="G9" s="87"/>
+      <c r="H9" s="87"/>
+      <c r="I9" s="87"/>
+      <c r="J9" s="88"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="174"/>
-      <c r="B10" s="175"/>
-      <c r="C10" s="175"/>
-      <c r="D10" s="175"/>
-      <c r="E10" s="175"/>
-      <c r="F10" s="175"/>
-      <c r="G10" s="175"/>
-      <c r="H10" s="175"/>
-      <c r="I10" s="175"/>
-      <c r="J10" s="176"/>
+      <c r="A10" s="86"/>
+      <c r="B10" s="87"/>
+      <c r="C10" s="87"/>
+      <c r="D10" s="87"/>
+      <c r="E10" s="87"/>
+      <c r="F10" s="87"/>
+      <c r="G10" s="87"/>
+      <c r="H10" s="87"/>
+      <c r="I10" s="87"/>
+      <c r="J10" s="88"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="174"/>
-      <c r="B11" s="175"/>
-      <c r="C11" s="175"/>
-      <c r="D11" s="175"/>
-      <c r="E11" s="175"/>
-      <c r="F11" s="175"/>
-      <c r="G11" s="175"/>
-      <c r="H11" s="175"/>
-      <c r="I11" s="175"/>
-      <c r="J11" s="176"/>
+      <c r="A11" s="86"/>
+      <c r="B11" s="87"/>
+      <c r="C11" s="87"/>
+      <c r="D11" s="87"/>
+      <c r="E11" s="87"/>
+      <c r="F11" s="87"/>
+      <c r="G11" s="87"/>
+      <c r="H11" s="87"/>
+      <c r="I11" s="87"/>
+      <c r="J11" s="88"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="174"/>
-      <c r="B12" s="175"/>
-      <c r="C12" s="175"/>
-      <c r="D12" s="175"/>
-      <c r="E12" s="175"/>
-      <c r="F12" s="175"/>
-      <c r="G12" s="175"/>
-      <c r="H12" s="175"/>
-      <c r="I12" s="175"/>
-      <c r="J12" s="176"/>
+      <c r="A12" s="86"/>
+      <c r="B12" s="87"/>
+      <c r="C12" s="87"/>
+      <c r="D12" s="87"/>
+      <c r="E12" s="87"/>
+      <c r="F12" s="87"/>
+      <c r="G12" s="87"/>
+      <c r="H12" s="87"/>
+      <c r="I12" s="87"/>
+      <c r="J12" s="88"/>
     </row>
     <row r="13" spans="1:10" ht="93" customHeight="1">
-      <c r="A13" s="174"/>
-      <c r="B13" s="175"/>
-      <c r="C13" s="175"/>
-      <c r="D13" s="175"/>
-      <c r="E13" s="175"/>
-      <c r="F13" s="175"/>
-      <c r="G13" s="175"/>
-      <c r="H13" s="175"/>
-      <c r="I13" s="175"/>
-      <c r="J13" s="176"/>
+      <c r="A13" s="86"/>
+      <c r="B13" s="87"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="87"/>
+      <c r="E13" s="87"/>
+      <c r="F13" s="87"/>
+      <c r="G13" s="87"/>
+      <c r="H13" s="87"/>
+      <c r="I13" s="87"/>
+      <c r="J13" s="88"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="170" t="s">
+      <c r="A14" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="90"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="90"/>
-      <c r="E14" s="90"/>
-      <c r="F14" s="90"/>
-      <c r="G14" s="90"/>
-      <c r="H14" s="90"/>
-      <c r="I14" s="90"/>
-      <c r="J14" s="171"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="55"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="170" t="s">
+      <c r="A15" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="90"/>
-      <c r="C15" s="91"/>
-      <c r="D15" s="121" t="s">
+      <c r="B15" s="54"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="90"/>
-      <c r="F15" s="90"/>
-      <c r="G15" s="90"/>
-      <c r="H15" s="91"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="69"/>
       <c r="I15" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="177" t="s">
+      <c r="J15" s="50" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="170" t="s">
+      <c r="A16" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="90"/>
-      <c r="C16" s="91"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="69"/>
       <c r="D16" s="13" t="s">
         <v>26</v>
       </c>
@@ -8035,18 +8373,18 @@
       <c r="G16" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="122" t="s">
+      <c r="H16" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="90"/>
-      <c r="J16" s="171"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="55"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="178">
+      <c r="A17" s="68">
         <v>1</v>
       </c>
-      <c r="B17" s="90"/>
-      <c r="C17" s="91"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="69"/>
       <c r="D17" s="14" t="s">
         <v>88</v>
       </c>
@@ -8059,18 +8397,18 @@
       <c r="G17" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="H17" s="121" t="s">
+      <c r="H17" s="53" t="s">
         <v>71</v>
       </c>
-      <c r="I17" s="90"/>
-      <c r="J17" s="171"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="55"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="178">
+      <c r="A18" s="68">
         <v>2</v>
       </c>
-      <c r="B18" s="90"/>
-      <c r="C18" s="91"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="69"/>
       <c r="D18" s="14" t="s">
         <v>91</v>
       </c>
@@ -8083,62 +8421,64 @@
       <c r="G18" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="H18" s="121"/>
-      <c r="I18" s="90"/>
-      <c r="J18" s="171"/>
+      <c r="H18" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="I18" s="54"/>
+      <c r="J18" s="55"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="178"/>
-      <c r="B19" s="90"/>
-      <c r="C19" s="91"/>
+      <c r="A19" s="68"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="69"/>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
       <c r="F19" s="15"/>
       <c r="G19" s="15"/>
-      <c r="H19" s="121"/>
-      <c r="I19" s="90"/>
-      <c r="J19" s="171"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="55"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="170" t="s">
+      <c r="A20" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="162"/>
-      <c r="C20" s="162"/>
-      <c r="D20" s="162"/>
-      <c r="E20" s="162"/>
-      <c r="F20" s="162"/>
-      <c r="G20" s="162"/>
-      <c r="H20" s="162"/>
-      <c r="I20" s="162"/>
-      <c r="J20" s="179"/>
+      <c r="B20" s="63"/>
+      <c r="C20" s="63"/>
+      <c r="D20" s="63"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="63"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="64"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="170" t="s">
+      <c r="A21" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="162"/>
-      <c r="C21" s="163"/>
-      <c r="D21" s="121" t="s">
+      <c r="B21" s="63"/>
+      <c r="C21" s="70"/>
+      <c r="D21" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="E21" s="159"/>
-      <c r="F21" s="159"/>
-      <c r="G21" s="159"/>
-      <c r="H21" s="164"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="65"/>
+      <c r="H21" s="66"/>
       <c r="I21" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="177" t="s">
+      <c r="J21" s="50" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="180" t="s">
+      <c r="A22" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="160"/>
-      <c r="C22" s="161"/>
+      <c r="B22" s="72"/>
+      <c r="C22" s="73"/>
       <c r="D22" s="13" t="s">
         <v>26</v>
       </c>
@@ -8151,103 +8491,107 @@
       <c r="G22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="H22" s="122" t="s">
+      <c r="H22" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="I22" s="162"/>
-      <c r="J22" s="179"/>
+      <c r="I22" s="63"/>
+      <c r="J22" s="64"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="181">
-        <v>1</v>
-      </c>
-      <c r="B23" s="124"/>
-      <c r="C23" s="124"/>
+      <c r="A23" s="103">
+        <v>3</v>
+      </c>
+      <c r="B23" s="104"/>
+      <c r="C23" s="104"/>
       <c r="D23" s="33" t="s">
         <v>94</v>
       </c>
       <c r="E23" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="F23" s="34"/>
+      <c r="F23" s="34" t="s">
+        <v>69</v>
+      </c>
       <c r="G23" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="H23" s="121"/>
-      <c r="I23" s="90"/>
-      <c r="J23" s="171"/>
+      <c r="H23" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="I23" s="54"/>
+      <c r="J23" s="55"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="181"/>
-      <c r="B24" s="124"/>
-      <c r="C24" s="124"/>
+      <c r="A24" s="103"/>
+      <c r="B24" s="104"/>
+      <c r="C24" s="104"/>
       <c r="D24" s="33"/>
       <c r="E24" s="33"/>
       <c r="F24" s="34"/>
       <c r="G24" s="34"/>
-      <c r="H24" s="121"/>
-      <c r="I24" s="90"/>
-      <c r="J24" s="171"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="55"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="182"/>
-      <c r="B25" s="146"/>
-      <c r="C25" s="146"/>
-      <c r="D25" s="147"/>
-      <c r="E25" s="147"/>
-      <c r="F25" s="148"/>
-      <c r="G25" s="148"/>
-      <c r="H25" s="149"/>
-      <c r="I25" s="129"/>
-      <c r="J25" s="173"/>
+      <c r="A25" s="79"/>
+      <c r="B25" s="80"/>
+      <c r="C25" s="80"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
+      <c r="H25" s="93"/>
+      <c r="I25" s="84"/>
+      <c r="J25" s="85"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="183"/>
-      <c r="B26" s="155"/>
-      <c r="C26" s="156"/>
-      <c r="D26" s="152"/>
-      <c r="E26" s="152"/>
-      <c r="F26" s="152"/>
-      <c r="G26" s="152"/>
-      <c r="H26" s="157"/>
-      <c r="I26" s="158"/>
-      <c r="J26" s="184"/>
+      <c r="A26" s="56"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="58"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="60"/>
+      <c r="J26" s="61"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="185"/>
-      <c r="B27" s="150"/>
-      <c r="C27" s="150"/>
-      <c r="D27" s="151"/>
-      <c r="E27" s="152"/>
-      <c r="F27" s="152"/>
-      <c r="G27" s="152"/>
-      <c r="H27" s="157"/>
-      <c r="I27" s="158"/>
-      <c r="J27" s="184"/>
+      <c r="A27" s="103"/>
+      <c r="B27" s="104"/>
+      <c r="C27" s="104"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="60"/>
+      <c r="J27" s="61"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="185"/>
-      <c r="B28" s="150"/>
-      <c r="C28" s="150"/>
-      <c r="D28" s="153"/>
-      <c r="E28" s="153"/>
-      <c r="F28" s="153"/>
-      <c r="G28" s="153"/>
-      <c r="H28" s="154"/>
-      <c r="I28" s="155"/>
-      <c r="J28" s="186"/>
+      <c r="A28" s="103"/>
+      <c r="B28" s="104"/>
+      <c r="C28" s="104"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="105"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="106"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A29" s="187"/>
-      <c r="B29" s="188"/>
-      <c r="C29" s="188"/>
-      <c r="D29" s="189"/>
-      <c r="E29" s="189"/>
-      <c r="F29" s="190"/>
-      <c r="G29" s="190"/>
-      <c r="H29" s="191"/>
-      <c r="I29" s="188"/>
-      <c r="J29" s="192"/>
+      <c r="A29" s="107"/>
+      <c r="B29" s="108"/>
+      <c r="C29" s="108"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="109"/>
+      <c r="I29" s="108"/>
+      <c r="J29" s="110"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9224,18 +9568,16 @@
     <row r="1002" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -9252,20 +9594,22 @@
     <mergeCell ref="H18:J18"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H25:J25"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9285,182 +9629,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="186" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="112" t="s">
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="112" t="s">
+      <c r="H1" s="176"/>
+      <c r="I1" s="176"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="112" t="s">
+      <c r="L1" s="176"/>
+      <c r="M1" s="176"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="112" t="s">
+      <c r="P1" s="78"/>
+      <c r="Q1" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="113"/>
-      <c r="S1" s="112" t="s">
+      <c r="R1" s="78"/>
+      <c r="S1" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="128"/>
+      <c r="T1" s="178"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="107"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="129"/>
-      <c r="J2" s="115"/>
-      <c r="K2" s="114"/>
-      <c r="L2" s="129"/>
-      <c r="M2" s="129"/>
-      <c r="N2" s="115"/>
-      <c r="O2" s="114"/>
-      <c r="P2" s="115"/>
-      <c r="Q2" s="114"/>
-      <c r="R2" s="115"/>
-      <c r="S2" s="114"/>
-      <c r="T2" s="130"/>
+      <c r="A2" s="102"/>
+      <c r="B2" s="87"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="90"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="90"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="90"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="183"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="107"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="116"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="108"/>
-      <c r="K3" s="116"/>
-      <c r="L3" s="93"/>
-      <c r="M3" s="93"/>
-      <c r="N3" s="108"/>
-      <c r="O3" s="116"/>
-      <c r="P3" s="108"/>
-      <c r="Q3" s="116"/>
-      <c r="R3" s="108"/>
-      <c r="S3" s="116"/>
-      <c r="T3" s="131"/>
+      <c r="A3" s="102"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="87"/>
+      <c r="I3" s="87"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="91"/>
+      <c r="L3" s="87"/>
+      <c r="M3" s="87"/>
+      <c r="N3" s="92"/>
+      <c r="O3" s="91"/>
+      <c r="P3" s="92"/>
+      <c r="Q3" s="91"/>
+      <c r="R3" s="92"/>
+      <c r="S3" s="91"/>
+      <c r="T3" s="184"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="109"/>
-      <c r="B4" s="110"/>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
-      <c r="K4" s="117"/>
-      <c r="L4" s="110"/>
-      <c r="M4" s="110"/>
-      <c r="N4" s="111"/>
-      <c r="O4" s="117"/>
-      <c r="P4" s="111"/>
-      <c r="Q4" s="117"/>
-      <c r="R4" s="111"/>
-      <c r="S4" s="117"/>
-      <c r="T4" s="138"/>
+      <c r="A4" s="119"/>
+      <c r="B4" s="120"/>
+      <c r="C4" s="120"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="120"/>
+      <c r="M4" s="120"/>
+      <c r="N4" s="121"/>
+      <c r="O4" s="122"/>
+      <c r="P4" s="121"/>
+      <c r="Q4" s="122"/>
+      <c r="R4" s="121"/>
+      <c r="S4" s="122"/>
+      <c r="T4" s="185"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="126" t="s">
+      <c r="A5" s="175" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="127"/>
-      <c r="C5" s="127"/>
-      <c r="D5" s="127"/>
-      <c r="E5" s="127"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="140" t="s">
+      <c r="B5" s="176"/>
+      <c r="C5" s="176"/>
+      <c r="D5" s="176"/>
+      <c r="E5" s="176"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="177" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="127"/>
-      <c r="I5" s="127"/>
-      <c r="J5" s="127"/>
-      <c r="K5" s="127"/>
-      <c r="L5" s="127"/>
-      <c r="M5" s="127"/>
-      <c r="N5" s="127"/>
-      <c r="O5" s="127"/>
-      <c r="P5" s="127"/>
-      <c r="Q5" s="127"/>
-      <c r="R5" s="127"/>
-      <c r="S5" s="127"/>
-      <c r="T5" s="128"/>
+      <c r="H5" s="176"/>
+      <c r="I5" s="176"/>
+      <c r="J5" s="176"/>
+      <c r="K5" s="176"/>
+      <c r="L5" s="176"/>
+      <c r="M5" s="176"/>
+      <c r="N5" s="176"/>
+      <c r="O5" s="176"/>
+      <c r="P5" s="176"/>
+      <c r="Q5" s="176"/>
+      <c r="R5" s="176"/>
+      <c r="S5" s="176"/>
+      <c r="T5" s="178"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="120" t="s">
+      <c r="A6" s="179" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="90"/>
-      <c r="C6" s="90"/>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="91"/>
-      <c r="G6" s="121" t="s">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90"/>
-      <c r="J6" s="90"/>
-      <c r="K6" s="90"/>
-      <c r="L6" s="90"/>
-      <c r="M6" s="90"/>
-      <c r="N6" s="90"/>
-      <c r="O6" s="90"/>
-      <c r="P6" s="90"/>
-      <c r="Q6" s="90"/>
-      <c r="R6" s="90"/>
-      <c r="S6" s="90"/>
-      <c r="T6" s="123"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="54"/>
+      <c r="M6" s="54"/>
+      <c r="N6" s="54"/>
+      <c r="O6" s="54"/>
+      <c r="P6" s="54"/>
+      <c r="Q6" s="54"/>
+      <c r="R6" s="54"/>
+      <c r="S6" s="54"/>
+      <c r="T6" s="180"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="120" t="s">
+      <c r="A7" s="179" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="90"/>
-      <c r="C7" s="90"/>
-      <c r="D7" s="90"/>
-      <c r="E7" s="90"/>
-      <c r="F7" s="91"/>
-      <c r="G7" s="121" t="s">
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="90"/>
-      <c r="I7" s="90"/>
-      <c r="J7" s="90"/>
-      <c r="K7" s="90"/>
-      <c r="L7" s="90"/>
-      <c r="M7" s="90"/>
-      <c r="N7" s="90"/>
-      <c r="O7" s="90"/>
-      <c r="P7" s="90"/>
-      <c r="Q7" s="90"/>
-      <c r="R7" s="90"/>
-      <c r="S7" s="90"/>
-      <c r="T7" s="123"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="54"/>
+      <c r="L7" s="54"/>
+      <c r="M7" s="54"/>
+      <c r="N7" s="54"/>
+      <c r="O7" s="54"/>
+      <c r="P7" s="54"/>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="54"/>
+      <c r="T7" s="180"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -9659,37 +10003,37 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="120" t="s">
+      <c r="A15" s="179" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="91"/>
-      <c r="C15" s="143" t="s">
+      <c r="B15" s="69"/>
+      <c r="C15" s="182" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="91"/>
-      <c r="E15" s="122" t="s">
+      <c r="D15" s="69"/>
+      <c r="E15" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="91"/>
-      <c r="G15" s="122" t="s">
+      <c r="F15" s="69"/>
+      <c r="G15" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="90"/>
-      <c r="I15" s="91"/>
-      <c r="J15" s="122" t="s">
+      <c r="H15" s="54"/>
+      <c r="I15" s="69"/>
+      <c r="J15" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="K15" s="91"/>
-      <c r="L15" s="122" t="s">
+      <c r="K15" s="69"/>
+      <c r="L15" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="M15" s="90"/>
-      <c r="N15" s="91"/>
-      <c r="O15" s="122" t="s">
+      <c r="M15" s="54"/>
+      <c r="N15" s="69"/>
+      <c r="O15" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="P15" s="90"/>
-      <c r="Q15" s="91"/>
+      <c r="P15" s="54"/>
+      <c r="Q15" s="69"/>
       <c r="R15" s="13" t="s">
         <v>48</v>
       </c>
@@ -9701,37 +10045,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="141">
+      <c r="A16" s="167">
         <v>1</v>
       </c>
-      <c r="B16" s="91"/>
-      <c r="C16" s="142" t="s">
+      <c r="B16" s="69"/>
+      <c r="C16" s="168" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="91"/>
-      <c r="E16" s="142" t="s">
+      <c r="D16" s="69"/>
+      <c r="E16" s="168" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="91"/>
-      <c r="G16" s="132" t="s">
+      <c r="F16" s="69"/>
+      <c r="G16" s="181" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="90"/>
-      <c r="I16" s="91"/>
-      <c r="J16" s="132" t="s">
+      <c r="H16" s="54"/>
+      <c r="I16" s="69"/>
+      <c r="J16" s="181" t="s">
         <v>54</v>
       </c>
-      <c r="K16" s="91"/>
-      <c r="L16" s="136" t="s">
+      <c r="K16" s="69"/>
+      <c r="L16" s="172" t="s">
         <v>55</v>
       </c>
-      <c r="M16" s="90"/>
-      <c r="N16" s="91"/>
-      <c r="O16" s="136" t="s">
+      <c r="M16" s="54"/>
+      <c r="N16" s="69"/>
+      <c r="O16" s="172" t="s">
         <v>56</v>
       </c>
-      <c r="P16" s="90"/>
-      <c r="Q16" s="91"/>
+      <c r="P16" s="54"/>
+      <c r="Q16" s="69"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
       <c r="T16" s="29"/>
@@ -9743,37 +10087,37 @@
       <c r="Z16" s="30"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="141">
+      <c r="A17" s="167">
         <v>2</v>
       </c>
-      <c r="B17" s="91"/>
-      <c r="C17" s="142" t="s">
+      <c r="B17" s="69"/>
+      <c r="C17" s="168" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="91"/>
-      <c r="E17" s="142" t="s">
+      <c r="D17" s="69"/>
+      <c r="E17" s="168" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="91"/>
-      <c r="G17" s="132" t="s">
+      <c r="F17" s="69"/>
+      <c r="G17" s="181" t="s">
         <v>59</v>
       </c>
-      <c r="H17" s="90"/>
-      <c r="I17" s="91"/>
-      <c r="J17" s="132" t="s">
+      <c r="H17" s="54"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="181" t="s">
         <v>60</v>
       </c>
-      <c r="K17" s="91"/>
-      <c r="L17" s="136" t="s">
+      <c r="K17" s="69"/>
+      <c r="L17" s="172" t="s">
         <v>61</v>
       </c>
-      <c r="M17" s="90"/>
-      <c r="N17" s="91"/>
-      <c r="O17" s="136" t="s">
+      <c r="M17" s="54"/>
+      <c r="N17" s="69"/>
+      <c r="O17" s="172" t="s">
         <v>62</v>
       </c>
-      <c r="P17" s="90"/>
-      <c r="Q17" s="91"/>
+      <c r="P17" s="54"/>
+      <c r="Q17" s="69"/>
       <c r="R17" s="28"/>
       <c r="S17" s="28"/>
       <c r="T17" s="29"/>
@@ -9785,23 +10129,23 @@
       <c r="Z17" s="30"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="141"/>
-      <c r="B18" s="91"/>
-      <c r="C18" s="142"/>
-      <c r="D18" s="91"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="91"/>
-      <c r="G18" s="132"/>
-      <c r="H18" s="90"/>
-      <c r="I18" s="91"/>
-      <c r="J18" s="132"/>
-      <c r="K18" s="91"/>
-      <c r="L18" s="136"/>
-      <c r="M18" s="90"/>
-      <c r="N18" s="91"/>
-      <c r="O18" s="136"/>
-      <c r="P18" s="90"/>
-      <c r="Q18" s="91"/>
+      <c r="A18" s="167"/>
+      <c r="B18" s="69"/>
+      <c r="C18" s="168"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="168"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="181"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="181"/>
+      <c r="K18" s="69"/>
+      <c r="L18" s="172"/>
+      <c r="M18" s="54"/>
+      <c r="N18" s="69"/>
+      <c r="O18" s="172"/>
+      <c r="P18" s="54"/>
+      <c r="Q18" s="69"/>
       <c r="R18" s="28"/>
       <c r="S18" s="28"/>
       <c r="T18" s="29"/>
@@ -9813,23 +10157,23 @@
       <c r="Z18" s="30"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="141"/>
-      <c r="B19" s="91"/>
-      <c r="C19" s="142"/>
-      <c r="D19" s="91"/>
-      <c r="E19" s="142"/>
-      <c r="F19" s="91"/>
-      <c r="G19" s="132"/>
-      <c r="H19" s="90"/>
-      <c r="I19" s="91"/>
-      <c r="J19" s="132"/>
-      <c r="K19" s="91"/>
-      <c r="L19" s="136"/>
-      <c r="M19" s="90"/>
-      <c r="N19" s="91"/>
-      <c r="O19" s="136"/>
-      <c r="P19" s="90"/>
-      <c r="Q19" s="91"/>
+      <c r="A19" s="167"/>
+      <c r="B19" s="69"/>
+      <c r="C19" s="168"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="168"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="181"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="69"/>
+      <c r="J19" s="181"/>
+      <c r="K19" s="69"/>
+      <c r="L19" s="172"/>
+      <c r="M19" s="54"/>
+      <c r="N19" s="69"/>
+      <c r="O19" s="172"/>
+      <c r="P19" s="54"/>
+      <c r="Q19" s="69"/>
       <c r="R19" s="28"/>
       <c r="S19" s="28"/>
       <c r="T19" s="29"/>
@@ -9841,23 +10185,23 @@
       <c r="Z19" s="30"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="141"/>
-      <c r="B20" s="91"/>
-      <c r="C20" s="142"/>
-      <c r="D20" s="91"/>
-      <c r="E20" s="142"/>
-      <c r="F20" s="91"/>
-      <c r="G20" s="132"/>
-      <c r="H20" s="90"/>
-      <c r="I20" s="91"/>
-      <c r="J20" s="132"/>
-      <c r="K20" s="91"/>
-      <c r="L20" s="136"/>
-      <c r="M20" s="90"/>
-      <c r="N20" s="91"/>
-      <c r="O20" s="136"/>
-      <c r="P20" s="90"/>
-      <c r="Q20" s="91"/>
+      <c r="A20" s="167"/>
+      <c r="B20" s="69"/>
+      <c r="C20" s="168"/>
+      <c r="D20" s="69"/>
+      <c r="E20" s="168"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="181"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="69"/>
+      <c r="J20" s="181"/>
+      <c r="K20" s="69"/>
+      <c r="L20" s="172"/>
+      <c r="M20" s="54"/>
+      <c r="N20" s="69"/>
+      <c r="O20" s="172"/>
+      <c r="P20" s="54"/>
+      <c r="Q20" s="69"/>
       <c r="R20" s="28"/>
       <c r="S20" s="28"/>
       <c r="T20" s="29"/>
@@ -9869,23 +10213,23 @@
       <c r="Z20" s="30"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="141"/>
-      <c r="B21" s="91"/>
-      <c r="C21" s="142"/>
-      <c r="D21" s="91"/>
-      <c r="E21" s="142"/>
-      <c r="F21" s="91"/>
-      <c r="G21" s="132"/>
-      <c r="H21" s="90"/>
-      <c r="I21" s="91"/>
-      <c r="J21" s="132"/>
-      <c r="K21" s="91"/>
-      <c r="L21" s="136"/>
-      <c r="M21" s="90"/>
-      <c r="N21" s="91"/>
-      <c r="O21" s="136"/>
-      <c r="P21" s="90"/>
-      <c r="Q21" s="91"/>
+      <c r="A21" s="167"/>
+      <c r="B21" s="69"/>
+      <c r="C21" s="168"/>
+      <c r="D21" s="69"/>
+      <c r="E21" s="168"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="181"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="69"/>
+      <c r="J21" s="181"/>
+      <c r="K21" s="69"/>
+      <c r="L21" s="172"/>
+      <c r="M21" s="54"/>
+      <c r="N21" s="69"/>
+      <c r="O21" s="172"/>
+      <c r="P21" s="54"/>
+      <c r="Q21" s="69"/>
       <c r="R21" s="28"/>
       <c r="S21" s="28"/>
       <c r="T21" s="29"/>
@@ -9897,23 +10241,23 @@
       <c r="Z21" s="30"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="141"/>
-      <c r="B22" s="91"/>
-      <c r="C22" s="142"/>
-      <c r="D22" s="91"/>
-      <c r="E22" s="142"/>
-      <c r="F22" s="91"/>
-      <c r="G22" s="132"/>
-      <c r="H22" s="90"/>
-      <c r="I22" s="91"/>
-      <c r="J22" s="132"/>
-      <c r="K22" s="91"/>
-      <c r="L22" s="136"/>
-      <c r="M22" s="90"/>
-      <c r="N22" s="91"/>
-      <c r="O22" s="136"/>
-      <c r="P22" s="90"/>
-      <c r="Q22" s="91"/>
+      <c r="A22" s="167"/>
+      <c r="B22" s="69"/>
+      <c r="C22" s="168"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="168"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="181"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="69"/>
+      <c r="J22" s="181"/>
+      <c r="K22" s="69"/>
+      <c r="L22" s="172"/>
+      <c r="M22" s="54"/>
+      <c r="N22" s="69"/>
+      <c r="O22" s="172"/>
+      <c r="P22" s="54"/>
+      <c r="Q22" s="69"/>
       <c r="R22" s="28"/>
       <c r="S22" s="28"/>
       <c r="T22" s="29"/>
@@ -9925,23 +10269,23 @@
       <c r="Z22" s="30"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="141"/>
-      <c r="B23" s="91"/>
-      <c r="C23" s="142"/>
-      <c r="D23" s="91"/>
-      <c r="E23" s="142"/>
-      <c r="F23" s="91"/>
-      <c r="G23" s="132"/>
-      <c r="H23" s="90"/>
-      <c r="I23" s="91"/>
-      <c r="J23" s="132"/>
-      <c r="K23" s="91"/>
-      <c r="L23" s="136"/>
-      <c r="M23" s="90"/>
-      <c r="N23" s="91"/>
-      <c r="O23" s="136"/>
-      <c r="P23" s="90"/>
-      <c r="Q23" s="91"/>
+      <c r="A23" s="167"/>
+      <c r="B23" s="69"/>
+      <c r="C23" s="168"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="168"/>
+      <c r="F23" s="69"/>
+      <c r="G23" s="181"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="69"/>
+      <c r="J23" s="181"/>
+      <c r="K23" s="69"/>
+      <c r="L23" s="172"/>
+      <c r="M23" s="54"/>
+      <c r="N23" s="69"/>
+      <c r="O23" s="172"/>
+      <c r="P23" s="54"/>
+      <c r="Q23" s="69"/>
       <c r="R23" s="28"/>
       <c r="S23" s="28"/>
       <c r="T23" s="29"/>
@@ -9953,23 +10297,23 @@
       <c r="Z23" s="30"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="141"/>
-      <c r="B24" s="91"/>
-      <c r="C24" s="142"/>
-      <c r="D24" s="91"/>
-      <c r="E24" s="142"/>
-      <c r="F24" s="91"/>
-      <c r="G24" s="132"/>
-      <c r="H24" s="90"/>
-      <c r="I24" s="91"/>
-      <c r="J24" s="132"/>
-      <c r="K24" s="91"/>
-      <c r="L24" s="136"/>
-      <c r="M24" s="90"/>
-      <c r="N24" s="91"/>
-      <c r="O24" s="136"/>
-      <c r="P24" s="90"/>
-      <c r="Q24" s="91"/>
+      <c r="A24" s="167"/>
+      <c r="B24" s="69"/>
+      <c r="C24" s="168"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="168"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="181"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="69"/>
+      <c r="J24" s="181"/>
+      <c r="K24" s="69"/>
+      <c r="L24" s="172"/>
+      <c r="M24" s="54"/>
+      <c r="N24" s="69"/>
+      <c r="O24" s="172"/>
+      <c r="P24" s="54"/>
+      <c r="Q24" s="69"/>
       <c r="R24" s="28"/>
       <c r="S24" s="28"/>
       <c r="T24" s="29"/>
@@ -9981,23 +10325,23 @@
       <c r="Z24" s="30"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="141"/>
-      <c r="B25" s="91"/>
-      <c r="C25" s="142"/>
-      <c r="D25" s="91"/>
-      <c r="E25" s="142"/>
-      <c r="F25" s="91"/>
-      <c r="G25" s="132"/>
-      <c r="H25" s="90"/>
-      <c r="I25" s="91"/>
-      <c r="J25" s="132"/>
-      <c r="K25" s="91"/>
-      <c r="L25" s="136"/>
-      <c r="M25" s="90"/>
-      <c r="N25" s="91"/>
-      <c r="O25" s="136"/>
-      <c r="P25" s="90"/>
-      <c r="Q25" s="91"/>
+      <c r="A25" s="167"/>
+      <c r="B25" s="69"/>
+      <c r="C25" s="168"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="168"/>
+      <c r="F25" s="69"/>
+      <c r="G25" s="181"/>
+      <c r="H25" s="54"/>
+      <c r="I25" s="69"/>
+      <c r="J25" s="181"/>
+      <c r="K25" s="69"/>
+      <c r="L25" s="172"/>
+      <c r="M25" s="54"/>
+      <c r="N25" s="69"/>
+      <c r="O25" s="172"/>
+      <c r="P25" s="54"/>
+      <c r="Q25" s="69"/>
       <c r="R25" s="28"/>
       <c r="S25" s="28"/>
       <c r="T25" s="29"/>
@@ -10009,23 +10353,23 @@
       <c r="Z25" s="30"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="141"/>
-      <c r="B26" s="91"/>
-      <c r="C26" s="142"/>
-      <c r="D26" s="91"/>
-      <c r="E26" s="142"/>
-      <c r="F26" s="91"/>
-      <c r="G26" s="132"/>
-      <c r="H26" s="90"/>
-      <c r="I26" s="91"/>
-      <c r="J26" s="132"/>
-      <c r="K26" s="91"/>
-      <c r="L26" s="136"/>
-      <c r="M26" s="90"/>
-      <c r="N26" s="91"/>
-      <c r="O26" s="136"/>
-      <c r="P26" s="90"/>
-      <c r="Q26" s="91"/>
+      <c r="A26" s="167"/>
+      <c r="B26" s="69"/>
+      <c r="C26" s="168"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="168"/>
+      <c r="F26" s="69"/>
+      <c r="G26" s="181"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="69"/>
+      <c r="J26" s="181"/>
+      <c r="K26" s="69"/>
+      <c r="L26" s="172"/>
+      <c r="M26" s="54"/>
+      <c r="N26" s="69"/>
+      <c r="O26" s="172"/>
+      <c r="P26" s="54"/>
+      <c r="Q26" s="69"/>
       <c r="R26" s="28"/>
       <c r="S26" s="28"/>
       <c r="T26" s="29"/>
@@ -10037,23 +10381,23 @@
       <c r="Z26" s="30"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="141"/>
-      <c r="B27" s="91"/>
-      <c r="C27" s="142"/>
-      <c r="D27" s="91"/>
-      <c r="E27" s="142"/>
-      <c r="F27" s="91"/>
-      <c r="G27" s="132"/>
-      <c r="H27" s="90"/>
-      <c r="I27" s="91"/>
-      <c r="J27" s="132"/>
-      <c r="K27" s="91"/>
-      <c r="L27" s="136"/>
-      <c r="M27" s="90"/>
-      <c r="N27" s="91"/>
-      <c r="O27" s="136"/>
-      <c r="P27" s="90"/>
-      <c r="Q27" s="91"/>
+      <c r="A27" s="167"/>
+      <c r="B27" s="69"/>
+      <c r="C27" s="168"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="168"/>
+      <c r="F27" s="69"/>
+      <c r="G27" s="181"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="69"/>
+      <c r="J27" s="181"/>
+      <c r="K27" s="69"/>
+      <c r="L27" s="172"/>
+      <c r="M27" s="54"/>
+      <c r="N27" s="69"/>
+      <c r="O27" s="172"/>
+      <c r="P27" s="54"/>
+      <c r="Q27" s="69"/>
       <c r="R27" s="28"/>
       <c r="S27" s="28"/>
       <c r="T27" s="29"/>
@@ -10065,23 +10409,23 @@
       <c r="Z27" s="30"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="141"/>
-      <c r="B28" s="91"/>
-      <c r="C28" s="142"/>
-      <c r="D28" s="91"/>
-      <c r="E28" s="142"/>
-      <c r="F28" s="91"/>
-      <c r="G28" s="132"/>
-      <c r="H28" s="90"/>
-      <c r="I28" s="91"/>
-      <c r="J28" s="132"/>
-      <c r="K28" s="91"/>
-      <c r="L28" s="136"/>
-      <c r="M28" s="90"/>
-      <c r="N28" s="91"/>
-      <c r="O28" s="136"/>
-      <c r="P28" s="90"/>
-      <c r="Q28" s="91"/>
+      <c r="A28" s="167"/>
+      <c r="B28" s="69"/>
+      <c r="C28" s="168"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="168"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="181"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="69"/>
+      <c r="J28" s="181"/>
+      <c r="K28" s="69"/>
+      <c r="L28" s="172"/>
+      <c r="M28" s="54"/>
+      <c r="N28" s="69"/>
+      <c r="O28" s="172"/>
+      <c r="P28" s="54"/>
+      <c r="Q28" s="69"/>
       <c r="R28" s="28"/>
       <c r="S28" s="28"/>
       <c r="T28" s="29"/>
@@ -10093,23 +10437,23 @@
       <c r="Z28" s="30"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="141"/>
-      <c r="B29" s="91"/>
-      <c r="C29" s="142"/>
-      <c r="D29" s="91"/>
-      <c r="E29" s="142"/>
-      <c r="F29" s="91"/>
-      <c r="G29" s="132"/>
-      <c r="H29" s="90"/>
-      <c r="I29" s="91"/>
-      <c r="J29" s="132"/>
-      <c r="K29" s="91"/>
-      <c r="L29" s="136"/>
-      <c r="M29" s="90"/>
-      <c r="N29" s="91"/>
-      <c r="O29" s="136"/>
-      <c r="P29" s="90"/>
-      <c r="Q29" s="91"/>
+      <c r="A29" s="167"/>
+      <c r="B29" s="69"/>
+      <c r="C29" s="168"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="168"/>
+      <c r="F29" s="69"/>
+      <c r="G29" s="181"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="69"/>
+      <c r="J29" s="181"/>
+      <c r="K29" s="69"/>
+      <c r="L29" s="172"/>
+      <c r="M29" s="54"/>
+      <c r="N29" s="69"/>
+      <c r="O29" s="172"/>
+      <c r="P29" s="54"/>
+      <c r="Q29" s="69"/>
       <c r="R29" s="28"/>
       <c r="S29" s="28"/>
       <c r="T29" s="29"/>
@@ -10121,23 +10465,23 @@
       <c r="Z29" s="30"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="141"/>
-      <c r="B30" s="91"/>
-      <c r="C30" s="142"/>
-      <c r="D30" s="91"/>
-      <c r="E30" s="142"/>
-      <c r="F30" s="91"/>
-      <c r="G30" s="132"/>
-      <c r="H30" s="90"/>
-      <c r="I30" s="91"/>
-      <c r="J30" s="132"/>
-      <c r="K30" s="91"/>
-      <c r="L30" s="136"/>
-      <c r="M30" s="90"/>
-      <c r="N30" s="91"/>
-      <c r="O30" s="136"/>
-      <c r="P30" s="90"/>
-      <c r="Q30" s="91"/>
+      <c r="A30" s="167"/>
+      <c r="B30" s="69"/>
+      <c r="C30" s="168"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="168"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="181"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="69"/>
+      <c r="J30" s="181"/>
+      <c r="K30" s="69"/>
+      <c r="L30" s="172"/>
+      <c r="M30" s="54"/>
+      <c r="N30" s="69"/>
+      <c r="O30" s="172"/>
+      <c r="P30" s="54"/>
+      <c r="Q30" s="69"/>
       <c r="R30" s="28"/>
       <c r="S30" s="28"/>
       <c r="T30" s="29"/>
@@ -10149,23 +10493,23 @@
       <c r="Z30" s="30"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="144"/>
-      <c r="B31" s="135"/>
-      <c r="C31" s="145"/>
-      <c r="D31" s="135"/>
-      <c r="E31" s="145"/>
-      <c r="F31" s="135"/>
-      <c r="G31" s="133"/>
-      <c r="H31" s="134"/>
-      <c r="I31" s="135"/>
-      <c r="J31" s="133"/>
-      <c r="K31" s="135"/>
-      <c r="L31" s="137"/>
-      <c r="M31" s="134"/>
-      <c r="N31" s="135"/>
-      <c r="O31" s="137"/>
-      <c r="P31" s="134"/>
-      <c r="Q31" s="135"/>
+      <c r="A31" s="169"/>
+      <c r="B31" s="170"/>
+      <c r="C31" s="171"/>
+      <c r="D31" s="170"/>
+      <c r="E31" s="171"/>
+      <c r="F31" s="170"/>
+      <c r="G31" s="187"/>
+      <c r="H31" s="174"/>
+      <c r="I31" s="170"/>
+      <c r="J31" s="187"/>
+      <c r="K31" s="170"/>
+      <c r="L31" s="173"/>
+      <c r="M31" s="174"/>
+      <c r="N31" s="170"/>
+      <c r="O31" s="173"/>
+      <c r="P31" s="174"/>
+      <c r="Q31" s="170"/>
       <c r="R31" s="31"/>
       <c r="S31" s="31"/>
       <c r="T31" s="32"/>
@@ -11163,6 +11507,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -11187,118 +11643,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/プロジェクト型演習_成果物_TasBo_コメント投稿.xlsx
+++ b/プロジェクト型演習_成果物_TasBo_コメント投稿.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TasBo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER111\Desktop\TasBoドキュメント\コメント投稿\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6DEB254-ACE8-457D-A9F5-D22DDD5820E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4C243A-0BDC-4E51-A6E2-62430791A782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="96">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -337,31 +337,6 @@
     <phoneticPr fontId="9"/>
   </si>
   <si>
-    <t>A1. コメントが未入力の場合（基本フロー5から分岐）
-a. システムはコメントが未入力であることを検出する。
-b. システムは「コメントを入力してください。」とエラーメッセージを表示する。
-c. システムはコメント一覧画面を再表示する。
-d. ユーザはコメントを入力する。
-e. 基本フロー5へ戻る。
-A2. コメントが文字数上限を超えている場合（基本フロー5から分岐）
-a. システムはコメントが文字数上限を超えていることを検出する。
-b. システムは「コメントは100文字以内で入力してください。」とエラーメッセージを表示する。
-c. システムはコメント一覧画面を再表示する。
-d. ユーザはコメントを修正する。
-e. 基本フロー5へ戻る。
-A3. 対象タスクが既に削除されている場合（基本フロー5または6から分岐）
-a. システムは対象タスクが存在しないことを検出する。
-b. システムは「対象のタスクは既に削除されています。」とエラーメッセージを表示する。
-c. システムはタスク一覧画面を表示する。
-d. ユースケースを終了する。
-A4. コメント登録処理中に対象タスクが削除された場合（基本フロー6から分岐）
-a. システムは対象タスクが存在しないことを検出する。
-b. システムは「対象のタスクは既に削除されています。」と表示する。
-c. システムはタスク一覧画面を表示する。
-d. ユースケースを終了する。</t>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
     <t>E1. データベース接続エラーまたはコメント登録処理中にシステムエラーが発生した場合。
 a. システムエラーが発生する。
 b. システムは「エラーが発生しました」とエラーメッセージを表示する。
@@ -377,24 +352,6 @@
     </rPh>
     <rPh sb="114" eb="116">
       <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="9"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-1.ユーザは対象タスクの「コメント閲覧」欄にある「コメント」リンクをクリックする。
-2.システムはコメント一覧画面を表示する。
-3.ユーザはコメント入力欄にコメントを入力する。
-4.ユーザは「投稿」ボタンを押下する。
-5.システムは入力内容の妥当性をチェックする。
-6. システムはコメント情報を登録する。
-7. システムは「コメントを投稿しました。」とメッセージを表示する。
-8. システムはコメント一覧を更新して表示する。</t>
-    <rPh sb="17" eb="19">
-      <t>エツラン</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>ラン</t>
     </rPh>
     <phoneticPr fontId="9"/>
   </si>
@@ -434,6 +391,41 @@
     <rPh sb="0" eb="1">
       <t>モド</t>
     </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>1.ユーザはタスク一覧画面で対象タスクの「コメント」リンクをクリックする。
+2.システムはコメント一覧画面を表示する。
+3.ユーザは「コメント投稿」ボタンを押下する。
+4.システムはコメント投稿フォーム画面を表示する。
+5.ユーザはコメントを入力する。
+6.ユーザは「投稿」ボタンを押下する。
+7.システムは入力内容の妥当性をチェックする。
+8.システムはコメント情報を登録する。
+9.システムは「コメントを投稿しました。」とメッセージを表示する。
+10.システムはコメント一覧画面を表示し、投稿したコメントを含むコメント一覧を表示する。</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>第二版</t>
+    <rPh sb="0" eb="3">
+      <t>ダイニハン</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>A1. コメントが未入力の場合（基本フロー6から分岐）
+a. システムはコメントが未入力であることを検出する。
+b. システムはコメント投稿フォーム画面に「コメントを入力してください。」とエラーメッセージを表示する。
+c. システムはコメント投稿フォーム画面を再表示する。
+A2. コメントが文字数上限を超えている場合（基本フロー6から分岐）
+a. システムはコメントが100文字を超えていることを検出する。
+b. システムはコメント投稿フォーム画面に「コメントは100文字以内で入力してください。」とエラーメッセージを表示する。
+c. システムはコメント投稿フォーム画面を再表示する。
+A3. コメント登録前または登録中に対象タスクが削除されていた場合（基本フロー3または6から分岐）
+a. システムは対象タスクが存在しないことを検出する。
+b. システムは「対象のタスクは既に削除されています。」とエラーメッセージを表示する。
+c. システムはコメント投稿フォーム画面を再表示する。</t>
     <phoneticPr fontId="9"/>
   </si>
 </sst>
@@ -1702,12 +1694,228 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="6" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1750,9 +1958,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1765,6 +1970,12 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1774,12 +1985,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1804,60 +2009,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="31" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1875,174 +2035,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="6" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2798,85 +2790,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="113" t="s">
+      <c r="C2" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
-      <c r="I2" s="114"/>
-      <c r="J2" s="114"/>
-      <c r="K2" s="114"/>
-      <c r="L2" s="114"/>
-      <c r="M2" s="114"/>
-      <c r="N2" s="114"/>
-      <c r="O2" s="114"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="101"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="87"/>
-      <c r="K3" s="87"/>
-      <c r="L3" s="87"/>
-      <c r="M3" s="87"/>
-      <c r="N3" s="87"/>
-      <c r="O3" s="87"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="99"/>
+      <c r="K3" s="99"/>
+      <c r="L3" s="99"/>
+      <c r="M3" s="99"/>
+      <c r="N3" s="99"/>
+      <c r="O3" s="99"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="87"/>
-      <c r="D4" s="87"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
-      <c r="J4" s="87"/>
-      <c r="K4" s="87"/>
-      <c r="L4" s="87"/>
-      <c r="M4" s="87"/>
-      <c r="N4" s="87"/>
-      <c r="O4" s="87"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="99"/>
+      <c r="K4" s="99"/>
+      <c r="L4" s="99"/>
+      <c r="M4" s="99"/>
+      <c r="N4" s="99"/>
+      <c r="O4" s="99"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="87"/>
-      <c r="D5" s="87"/>
-      <c r="E5" s="87"/>
-      <c r="F5" s="87"/>
-      <c r="G5" s="87"/>
-      <c r="H5" s="87"/>
-      <c r="I5" s="87"/>
-      <c r="J5" s="87"/>
-      <c r="K5" s="87"/>
-      <c r="L5" s="87"/>
-      <c r="M5" s="87"/>
-      <c r="N5" s="87"/>
-      <c r="O5" s="87"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="99"/>
+      <c r="J5" s="99"/>
+      <c r="K5" s="99"/>
+      <c r="L5" s="99"/>
+      <c r="M5" s="99"/>
+      <c r="N5" s="99"/>
+      <c r="O5" s="99"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="87"/>
-      <c r="D6" s="87"/>
-      <c r="E6" s="87"/>
-      <c r="F6" s="87"/>
-      <c r="G6" s="87"/>
-      <c r="H6" s="87"/>
-      <c r="I6" s="87"/>
-      <c r="J6" s="87"/>
-      <c r="K6" s="87"/>
-      <c r="L6" s="87"/>
-      <c r="M6" s="87"/>
-      <c r="N6" s="87"/>
-      <c r="O6" s="87"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="99"/>
+      <c r="F6" s="99"/>
+      <c r="G6" s="99"/>
+      <c r="H6" s="99"/>
+      <c r="I6" s="99"/>
+      <c r="J6" s="99"/>
+      <c r="K6" s="99"/>
+      <c r="L6" s="99"/>
+      <c r="M6" s="99"/>
+      <c r="N6" s="99"/>
+      <c r="O6" s="99"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2896,46 +2888,50 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="115" t="s">
+      <c r="E8" s="102" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="87"/>
-      <c r="G8" s="87"/>
-      <c r="H8" s="87"/>
-      <c r="I8" s="87"/>
-      <c r="J8" s="87"/>
-      <c r="K8" s="87"/>
-      <c r="L8" s="87"/>
-      <c r="M8" s="87"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="99"/>
+      <c r="J8" s="99"/>
+      <c r="K8" s="99"/>
+      <c r="L8" s="99"/>
+      <c r="M8" s="99"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="111" t="s">
+      <c r="G13" s="95" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="69"/>
-      <c r="I13" s="116">
+      <c r="H13" s="97"/>
+      <c r="I13" s="103">
         <v>46196</v>
       </c>
-      <c r="J13" s="54"/>
-      <c r="K13" s="69"/>
+      <c r="J13" s="96"/>
+      <c r="K13" s="97"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="111"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="116"/>
-      <c r="J14" s="54"/>
-      <c r="K14" s="69"/>
+      <c r="G14" s="95" t="s">
+        <v>94</v>
+      </c>
+      <c r="H14" s="97"/>
+      <c r="I14" s="103">
+        <v>46202</v>
+      </c>
+      <c r="J14" s="96"/>
+      <c r="K14" s="97"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="111"/>
-      <c r="H15" s="69"/>
-      <c r="I15" s="111"/>
-      <c r="J15" s="54"/>
-      <c r="K15" s="69"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="97"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="96"/>
+      <c r="K15" s="97"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2944,13 +2940,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="112" t="s">
+      <c r="G17" s="98" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="87"/>
-      <c r="I17" s="87"/>
-      <c r="J17" s="87"/>
-      <c r="K17" s="87"/>
+      <c r="H17" s="99"/>
+      <c r="I17" s="99"/>
+      <c r="J17" s="99"/>
+      <c r="K17" s="99"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3964,19 +3960,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="110" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="77" t="s">
+      <c r="B1" s="111"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="78"/>
-      <c r="F1" s="77" t="s">
+      <c r="E1" s="119"/>
+      <c r="F1" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="78"/>
+      <c r="G1" s="119"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -3988,40 +3984,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="102"/>
-      <c r="B2" s="87"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="96"/>
-      <c r="I2" s="96"/>
-      <c r="J2" s="97"/>
+      <c r="A2" s="113"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="120"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="121"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="104"/>
+      <c r="J2" s="107"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="102"/>
-      <c r="B3" s="87"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="95"/>
-      <c r="I3" s="95"/>
-      <c r="J3" s="98"/>
+      <c r="A3" s="113"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="114"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="114"/>
+      <c r="H3" s="105"/>
+      <c r="I3" s="105"/>
+      <c r="J3" s="108"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="119"/>
-      <c r="B4" s="120"/>
-      <c r="C4" s="121"/>
-      <c r="D4" s="122"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="122"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="118"/>
+      <c r="A4" s="115"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="109"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -5378,19 +5374,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="148" t="s">
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="131"/>
-      <c r="F1" s="148" t="s">
+      <c r="E1" s="61"/>
+      <c r="F1" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="131"/>
+      <c r="G1" s="61"/>
       <c r="H1" s="44" t="s">
         <v>5</v>
       </c>
@@ -5402,194 +5398,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="142"/>
-      <c r="B2" s="143"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="149" t="s">
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="150"/>
-      <c r="F2" s="149" t="s">
+      <c r="E2" s="80"/>
+      <c r="F2" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="150"/>
-      <c r="H2" s="153">
+      <c r="G2" s="80"/>
+      <c r="H2" s="83">
         <v>46195</v>
       </c>
-      <c r="I2" s="123" t="s">
+      <c r="I2" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="126"/>
+      <c r="J2" s="56"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="142"/>
-      <c r="B3" s="143"/>
-      <c r="C3" s="144"/>
-      <c r="D3" s="151"/>
-      <c r="E3" s="144"/>
-      <c r="F3" s="151"/>
-      <c r="G3" s="144"/>
-      <c r="H3" s="124"/>
-      <c r="I3" s="124"/>
-      <c r="J3" s="127"/>
+      <c r="A3" s="72"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="57"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="145"/>
-      <c r="B4" s="146"/>
-      <c r="C4" s="147"/>
-      <c r="D4" s="152"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="152"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="125"/>
-      <c r="I4" s="125"/>
-      <c r="J4" s="128"/>
+      <c r="A4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="58"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="129" t="s">
+      <c r="A5" s="59" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="130"/>
-      <c r="C5" s="131"/>
-      <c r="D5" s="132" t="s">
+      <c r="B5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="62" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="130"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="130"/>
-      <c r="H5" s="130"/>
-      <c r="I5" s="130"/>
-      <c r="J5" s="133"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="63"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="134" t="s">
+      <c r="A6" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="135"/>
-      <c r="C6" s="136"/>
-      <c r="D6" s="137" t="s">
+      <c r="B6" s="65"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="135"/>
-      <c r="F6" s="135"/>
-      <c r="G6" s="135"/>
-      <c r="H6" s="135"/>
-      <c r="I6" s="135"/>
-      <c r="J6" s="138"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="68"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="134" t="s">
+      <c r="A7" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="135"/>
-      <c r="C7" s="136"/>
-      <c r="D7" s="137" t="s">
+      <c r="B7" s="65"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="67" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="135"/>
-      <c r="F7" s="135"/>
-      <c r="G7" s="135"/>
-      <c r="H7" s="135"/>
-      <c r="I7" s="135"/>
-      <c r="J7" s="138"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
+      <c r="I7" s="65"/>
+      <c r="J7" s="68"/>
     </row>
     <row r="8" spans="1:10" ht="56.25" customHeight="1">
-      <c r="A8" s="134" t="s">
+      <c r="A8" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="135"/>
-      <c r="C8" s="136"/>
-      <c r="D8" s="154" t="s">
+      <c r="B8" s="65"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="84" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="135"/>
-      <c r="F8" s="135"/>
-      <c r="G8" s="135"/>
-      <c r="H8" s="135"/>
-      <c r="I8" s="135"/>
-      <c r="J8" s="138"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="65"/>
+      <c r="I8" s="65"/>
+      <c r="J8" s="68"/>
     </row>
     <row r="9" spans="1:10" ht="147.75" customHeight="1">
-      <c r="A9" s="155" t="s">
+      <c r="A9" s="91" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="158" t="s">
+      <c r="B9" s="94" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="136"/>
-      <c r="D9" s="154" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" s="135"/>
-      <c r="F9" s="135"/>
-      <c r="G9" s="135"/>
-      <c r="H9" s="135"/>
-      <c r="I9" s="135"/>
-      <c r="J9" s="138"/>
-    </row>
-    <row r="10" spans="1:10" ht="348" customHeight="1">
-      <c r="A10" s="156"/>
-      <c r="B10" s="158" t="s">
+      <c r="C9" s="66"/>
+      <c r="D9" s="84" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="68"/>
+    </row>
+    <row r="10" spans="1:10" ht="193.5" customHeight="1">
+      <c r="A10" s="92"/>
+      <c r="B10" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="136"/>
-      <c r="D10" s="154" t="s">
+      <c r="C10" s="66"/>
+      <c r="D10" s="84" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
+      <c r="G10" s="65"/>
+      <c r="H10" s="65"/>
+      <c r="I10" s="65"/>
+      <c r="J10" s="68"/>
+    </row>
+    <row r="11" spans="1:10" ht="102.75" customHeight="1">
+      <c r="A11" s="93"/>
+      <c r="B11" s="94" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="66"/>
+      <c r="D11" s="84" t="s">
         <v>84</v>
       </c>
-      <c r="E10" s="135"/>
-      <c r="F10" s="135"/>
-      <c r="G10" s="135"/>
-      <c r="H10" s="135"/>
-      <c r="I10" s="135"/>
-      <c r="J10" s="138"/>
-    </row>
-    <row r="11" spans="1:10" ht="102.75" customHeight="1">
-      <c r="A11" s="157"/>
-      <c r="B11" s="158" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="136"/>
-      <c r="D11" s="154" t="s">
-        <v>85</v>
-      </c>
-      <c r="E11" s="135"/>
-      <c r="F11" s="135"/>
-      <c r="G11" s="135"/>
-      <c r="H11" s="135"/>
-      <c r="I11" s="135"/>
-      <c r="J11" s="138"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="68"/>
     </row>
     <row r="12" spans="1:10" ht="46.5" customHeight="1">
-      <c r="A12" s="134" t="s">
+      <c r="A12" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="135"/>
-      <c r="C12" s="136"/>
-      <c r="D12" s="154" t="s">
+      <c r="B12" s="65"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="84" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="135"/>
-      <c r="F12" s="135"/>
-      <c r="G12" s="135"/>
-      <c r="H12" s="135"/>
-      <c r="I12" s="135"/>
-      <c r="J12" s="138"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="68"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="159" t="s">
+      <c r="A13" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="160"/>
-      <c r="C13" s="161"/>
-      <c r="D13" s="162" t="s">
+      <c r="B13" s="86"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="88" t="s">
         <v>83</v>
       </c>
-      <c r="E13" s="163"/>
-      <c r="F13" s="163"/>
-      <c r="G13" s="163"/>
-      <c r="H13" s="163"/>
-      <c r="I13" s="163"/>
-      <c r="J13" s="164"/>
+      <c r="E13" s="89"/>
+      <c r="F13" s="89"/>
+      <c r="G13" s="89"/>
+      <c r="H13" s="89"/>
+      <c r="I13" s="89"/>
+      <c r="J13" s="90"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -6626,19 +6622,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="124" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="148" t="s">
+      <c r="B1" s="70"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="131"/>
-      <c r="F1" s="148" t="s">
+      <c r="E1" s="61"/>
+      <c r="F1" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="131"/>
+      <c r="G1" s="61"/>
       <c r="H1" s="45" t="s">
         <v>5</v>
       </c>
@@ -6650,48 +6646,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="142"/>
-      <c r="B2" s="143"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="149" t="s">
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="150"/>
-      <c r="F2" s="149" t="s">
+      <c r="E2" s="80"/>
+      <c r="F2" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="G2" s="150"/>
-      <c r="H2" s="166">
+      <c r="G2" s="80"/>
+      <c r="H2" s="125">
         <v>46196</v>
       </c>
-      <c r="I2" s="123" t="s">
+      <c r="I2" s="53" t="s">
         <v>73</v>
       </c>
-      <c r="J2" s="126"/>
+      <c r="J2" s="56"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="142"/>
-      <c r="B3" s="143"/>
-      <c r="C3" s="144"/>
-      <c r="D3" s="151"/>
-      <c r="E3" s="144"/>
-      <c r="F3" s="151"/>
-      <c r="G3" s="144"/>
-      <c r="H3" s="124"/>
-      <c r="I3" s="124"/>
-      <c r="J3" s="127"/>
+      <c r="A3" s="72"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="57"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="145"/>
-      <c r="B4" s="146"/>
-      <c r="C4" s="147"/>
-      <c r="D4" s="152"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="152"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="125"/>
-      <c r="I4" s="125"/>
-      <c r="J4" s="128"/>
+      <c r="A4" s="75"/>
+      <c r="B4" s="76"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="58"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="42"/>
@@ -8140,19 +8136,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="110" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="77" t="s">
+      <c r="B1" s="111"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="78"/>
-      <c r="F1" s="77" t="s">
+      <c r="E1" s="119"/>
+      <c r="F1" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="78"/>
+      <c r="G1" s="119"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -8164,190 +8160,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="102"/>
-      <c r="B2" s="87"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="89" t="s">
+      <c r="A2" s="113"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="90"/>
-      <c r="F2" s="89" t="s">
+      <c r="E2" s="121"/>
+      <c r="F2" s="120" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="90"/>
-      <c r="H2" s="94">
+      <c r="G2" s="121"/>
+      <c r="H2" s="160">
         <v>46196</v>
       </c>
-      <c r="I2" s="96" t="s">
+      <c r="I2" s="104" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="97"/>
+      <c r="J2" s="107"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="102"/>
-      <c r="B3" s="87"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="91"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="95"/>
-      <c r="I3" s="95"/>
-      <c r="J3" s="98"/>
+      <c r="A3" s="113"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="114"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="114"/>
+      <c r="H3" s="105"/>
+      <c r="I3" s="105"/>
+      <c r="J3" s="108"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="102"/>
-      <c r="B4" s="87"/>
-      <c r="C4" s="92"/>
-      <c r="D4" s="91"/>
-      <c r="E4" s="92"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="95"/>
-      <c r="I4" s="95"/>
-      <c r="J4" s="98"/>
+      <c r="A4" s="113"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="105"/>
+      <c r="I4" s="105"/>
+      <c r="J4" s="108"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="147" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="81" t="s">
+      <c r="B5" s="148"/>
+      <c r="C5" s="149"/>
+      <c r="D5" s="152" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="82"/>
+      <c r="E5" s="148"/>
+      <c r="F5" s="148"/>
+      <c r="G5" s="148"/>
+      <c r="H5" s="148"/>
+      <c r="I5" s="148"/>
+      <c r="J5" s="153"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="62" t="s">
+      <c r="A6" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="55"/>
+      <c r="B6" s="96"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="96"/>
+      <c r="E6" s="96"/>
+      <c r="F6" s="96"/>
+      <c r="G6" s="96"/>
+      <c r="H6" s="96"/>
+      <c r="I6" s="96"/>
+      <c r="J6" s="127"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="83"/>
-      <c r="B7" s="84"/>
-      <c r="C7" s="84"/>
-      <c r="D7" s="84"/>
-      <c r="E7" s="84"/>
-      <c r="F7" s="84"/>
-      <c r="G7" s="84"/>
-      <c r="H7" s="84"/>
-      <c r="I7" s="84"/>
-      <c r="J7" s="85"/>
+      <c r="A7" s="154"/>
+      <c r="B7" s="155"/>
+      <c r="C7" s="155"/>
+      <c r="D7" s="155"/>
+      <c r="E7" s="155"/>
+      <c r="F7" s="155"/>
+      <c r="G7" s="155"/>
+      <c r="H7" s="155"/>
+      <c r="I7" s="155"/>
+      <c r="J7" s="156"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="86"/>
-      <c r="B8" s="87"/>
-      <c r="C8" s="87"/>
-      <c r="D8" s="87"/>
-      <c r="E8" s="87"/>
-      <c r="F8" s="87"/>
-      <c r="G8" s="87"/>
-      <c r="H8" s="87"/>
-      <c r="I8" s="87"/>
-      <c r="J8" s="88"/>
+      <c r="A8" s="157"/>
+      <c r="B8" s="99"/>
+      <c r="C8" s="99"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="99"/>
+      <c r="J8" s="158"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="86"/>
-      <c r="B9" s="87"/>
-      <c r="C9" s="87"/>
-      <c r="D9" s="87"/>
-      <c r="E9" s="87"/>
-      <c r="F9" s="87"/>
-      <c r="G9" s="87"/>
-      <c r="H9" s="87"/>
-      <c r="I9" s="87"/>
-      <c r="J9" s="88"/>
+      <c r="A9" s="157"/>
+      <c r="B9" s="99"/>
+      <c r="C9" s="99"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="99"/>
+      <c r="H9" s="99"/>
+      <c r="I9" s="99"/>
+      <c r="J9" s="158"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="86"/>
-      <c r="B10" s="87"/>
-      <c r="C10" s="87"/>
-      <c r="D10" s="87"/>
-      <c r="E10" s="87"/>
-      <c r="F10" s="87"/>
-      <c r="G10" s="87"/>
-      <c r="H10" s="87"/>
-      <c r="I10" s="87"/>
-      <c r="J10" s="88"/>
+      <c r="A10" s="157"/>
+      <c r="B10" s="99"/>
+      <c r="C10" s="99"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99"/>
+      <c r="H10" s="99"/>
+      <c r="I10" s="99"/>
+      <c r="J10" s="158"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="86"/>
-      <c r="B11" s="87"/>
-      <c r="C11" s="87"/>
-      <c r="D11" s="87"/>
-      <c r="E11" s="87"/>
-      <c r="F11" s="87"/>
-      <c r="G11" s="87"/>
-      <c r="H11" s="87"/>
-      <c r="I11" s="87"/>
-      <c r="J11" s="88"/>
+      <c r="A11" s="157"/>
+      <c r="B11" s="99"/>
+      <c r="C11" s="99"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="99"/>
+      <c r="I11" s="99"/>
+      <c r="J11" s="158"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="86"/>
-      <c r="B12" s="87"/>
-      <c r="C12" s="87"/>
-      <c r="D12" s="87"/>
-      <c r="E12" s="87"/>
-      <c r="F12" s="87"/>
-      <c r="G12" s="87"/>
-      <c r="H12" s="87"/>
-      <c r="I12" s="87"/>
-      <c r="J12" s="88"/>
+      <c r="A12" s="157"/>
+      <c r="B12" s="99"/>
+      <c r="C12" s="99"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="99"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="99"/>
+      <c r="I12" s="99"/>
+      <c r="J12" s="158"/>
     </row>
     <row r="13" spans="1:10" ht="93" customHeight="1">
-      <c r="A13" s="86"/>
-      <c r="B13" s="87"/>
-      <c r="C13" s="87"/>
-      <c r="D13" s="87"/>
-      <c r="E13" s="87"/>
-      <c r="F13" s="87"/>
-      <c r="G13" s="87"/>
-      <c r="H13" s="87"/>
-      <c r="I13" s="87"/>
-      <c r="J13" s="88"/>
+      <c r="A13" s="157"/>
+      <c r="B13" s="99"/>
+      <c r="C13" s="99"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="99"/>
+      <c r="I13" s="99"/>
+      <c r="J13" s="158"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="62" t="s">
+      <c r="A14" s="134" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="54"/>
-      <c r="J14" s="55"/>
+      <c r="B14" s="96"/>
+      <c r="C14" s="96"/>
+      <c r="D14" s="96"/>
+      <c r="E14" s="96"/>
+      <c r="F14" s="96"/>
+      <c r="G14" s="96"/>
+      <c r="H14" s="96"/>
+      <c r="I14" s="96"/>
+      <c r="J14" s="127"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="62" t="s">
+      <c r="A15" s="134" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="54"/>
-      <c r="C15" s="69"/>
-      <c r="D15" s="53" t="s">
-        <v>87</v>
-      </c>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="69"/>
+      <c r="B15" s="96"/>
+      <c r="C15" s="97"/>
+      <c r="D15" s="126" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" s="96"/>
+      <c r="F15" s="96"/>
+      <c r="G15" s="96"/>
+      <c r="H15" s="97"/>
       <c r="I15" s="13" t="s">
         <v>24</v>
       </c>
@@ -8356,11 +8352,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="62" t="s">
+      <c r="A16" s="134" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="54"/>
-      <c r="C16" s="69"/>
+      <c r="B16" s="96"/>
+      <c r="C16" s="97"/>
       <c r="D16" s="13" t="s">
         <v>26</v>
       </c>
@@ -8373,44 +8369,44 @@
       <c r="G16" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="67" t="s">
+      <c r="H16" s="139" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="54"/>
-      <c r="J16" s="55"/>
+      <c r="I16" s="96"/>
+      <c r="J16" s="127"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="68">
+      <c r="A17" s="140">
         <v>1</v>
       </c>
-      <c r="B17" s="54"/>
-      <c r="C17" s="69"/>
+      <c r="B17" s="96"/>
+      <c r="C17" s="97"/>
       <c r="D17" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" s="15" t="s">
         <v>88</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>90</v>
       </c>
       <c r="G17" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="H17" s="53" t="s">
+      <c r="H17" s="126" t="s">
         <v>71</v>
       </c>
-      <c r="I17" s="54"/>
-      <c r="J17" s="55"/>
+      <c r="I17" s="96"/>
+      <c r="J17" s="127"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="68">
+      <c r="A18" s="140">
         <v>2</v>
       </c>
-      <c r="B18" s="54"/>
-      <c r="C18" s="69"/>
+      <c r="B18" s="96"/>
+      <c r="C18" s="97"/>
       <c r="D18" s="14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E18" s="14" t="s">
         <v>70</v>
@@ -8419,53 +8415,53 @@
         <v>69</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="H18" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="H18" s="126" t="s">
         <v>69</v>
       </c>
-      <c r="I18" s="54"/>
-      <c r="J18" s="55"/>
+      <c r="I18" s="96"/>
+      <c r="J18" s="127"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="68"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="69"/>
+      <c r="A19" s="140"/>
+      <c r="B19" s="96"/>
+      <c r="C19" s="97"/>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
       <c r="F19" s="15"/>
       <c r="G19" s="15"/>
-      <c r="H19" s="53"/>
-      <c r="I19" s="54"/>
-      <c r="J19" s="55"/>
+      <c r="H19" s="126"/>
+      <c r="I19" s="96"/>
+      <c r="J19" s="127"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="62" t="s">
+      <c r="A20" s="134" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="63"/>
-      <c r="C20" s="63"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="63"/>
-      <c r="G20" s="63"/>
-      <c r="H20" s="63"/>
-      <c r="I20" s="63"/>
-      <c r="J20" s="64"/>
+      <c r="B20" s="135"/>
+      <c r="C20" s="135"/>
+      <c r="D20" s="135"/>
+      <c r="E20" s="135"/>
+      <c r="F20" s="135"/>
+      <c r="G20" s="135"/>
+      <c r="H20" s="135"/>
+      <c r="I20" s="135"/>
+      <c r="J20" s="136"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="62" t="s">
+      <c r="A21" s="134" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="63"/>
-      <c r="C21" s="70"/>
-      <c r="D21" s="53" t="s">
-        <v>93</v>
-      </c>
-      <c r="E21" s="65"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="66"/>
+      <c r="B21" s="135"/>
+      <c r="C21" s="141"/>
+      <c r="D21" s="126" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" s="137"/>
+      <c r="F21" s="137"/>
+      <c r="G21" s="137"/>
+      <c r="H21" s="138"/>
       <c r="I21" s="13" t="s">
         <v>24</v>
       </c>
@@ -8474,11 +8470,11 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="71" t="s">
+      <c r="A22" s="142" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="72"/>
-      <c r="C22" s="73"/>
+      <c r="B22" s="143"/>
+      <c r="C22" s="144"/>
       <c r="D22" s="13" t="s">
         <v>26</v>
       </c>
@@ -8491,20 +8487,20 @@
       <c r="G22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="H22" s="67" t="s">
+      <c r="H22" s="139" t="s">
         <v>16</v>
       </c>
-      <c r="I22" s="63"/>
-      <c r="J22" s="64"/>
+      <c r="I22" s="135"/>
+      <c r="J22" s="136"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="103">
+      <c r="A23" s="145">
         <v>3</v>
       </c>
-      <c r="B23" s="104"/>
-      <c r="C23" s="104"/>
+      <c r="B23" s="146"/>
+      <c r="C23" s="146"/>
       <c r="D23" s="33" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E23" s="33" t="s">
         <v>70</v>
@@ -8513,85 +8509,85 @@
         <v>69</v>
       </c>
       <c r="G23" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="H23" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="H23" s="126" t="s">
         <v>69</v>
       </c>
-      <c r="I23" s="54"/>
-      <c r="J23" s="55"/>
+      <c r="I23" s="96"/>
+      <c r="J23" s="127"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="103"/>
-      <c r="B24" s="104"/>
-      <c r="C24" s="104"/>
+      <c r="A24" s="145"/>
+      <c r="B24" s="146"/>
+      <c r="C24" s="146"/>
       <c r="D24" s="33"/>
       <c r="E24" s="33"/>
       <c r="F24" s="34"/>
       <c r="G24" s="34"/>
-      <c r="H24" s="53"/>
-      <c r="I24" s="54"/>
-      <c r="J24" s="55"/>
+      <c r="H24" s="126"/>
+      <c r="I24" s="96"/>
+      <c r="J24" s="127"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="79"/>
-      <c r="B25" s="80"/>
-      <c r="C25" s="80"/>
+      <c r="A25" s="150"/>
+      <c r="B25" s="151"/>
+      <c r="C25" s="151"/>
       <c r="D25" s="48"/>
       <c r="E25" s="48"/>
       <c r="F25" s="49"/>
       <c r="G25" s="49"/>
-      <c r="H25" s="93"/>
-      <c r="I25" s="84"/>
-      <c r="J25" s="85"/>
+      <c r="H25" s="159"/>
+      <c r="I25" s="155"/>
+      <c r="J25" s="156"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="56"/>
-      <c r="B26" s="57"/>
-      <c r="C26" s="58"/>
+      <c r="A26" s="128"/>
+      <c r="B26" s="129"/>
+      <c r="C26" s="130"/>
       <c r="D26" s="47"/>
       <c r="E26" s="47"/>
       <c r="F26" s="47"/>
       <c r="G26" s="47"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="60"/>
-      <c r="J26" s="61"/>
+      <c r="H26" s="131"/>
+      <c r="I26" s="132"/>
+      <c r="J26" s="133"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="103"/>
-      <c r="B27" s="104"/>
-      <c r="C27" s="104"/>
+      <c r="A27" s="145"/>
+      <c r="B27" s="146"/>
+      <c r="C27" s="146"/>
       <c r="D27" s="34"/>
       <c r="E27" s="47"/>
       <c r="F27" s="47"/>
       <c r="G27" s="47"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="60"/>
-      <c r="J27" s="61"/>
+      <c r="H27" s="131"/>
+      <c r="I27" s="132"/>
+      <c r="J27" s="133"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="103"/>
-      <c r="B28" s="104"/>
-      <c r="C28" s="104"/>
+      <c r="A28" s="145"/>
+      <c r="B28" s="146"/>
+      <c r="C28" s="146"/>
       <c r="D28" s="33"/>
       <c r="E28" s="33"/>
       <c r="F28" s="33"/>
       <c r="G28" s="33"/>
-      <c r="H28" s="105"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="106"/>
+      <c r="H28" s="161"/>
+      <c r="I28" s="129"/>
+      <c r="J28" s="162"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A29" s="107"/>
-      <c r="B29" s="108"/>
-      <c r="C29" s="108"/>
+      <c r="A29" s="163"/>
+      <c r="B29" s="164"/>
+      <c r="C29" s="164"/>
       <c r="D29" s="51"/>
       <c r="E29" s="51"/>
       <c r="F29" s="52"/>
       <c r="G29" s="52"/>
-      <c r="H29" s="109"/>
-      <c r="I29" s="108"/>
-      <c r="J29" s="110"/>
+      <c r="H29" s="165"/>
+      <c r="I29" s="164"/>
+      <c r="J29" s="166"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9632,100 +9628,100 @@
       <c r="A1" s="186" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="77" t="s">
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="118" t="s">
         <v>3</v>
       </c>
       <c r="H1" s="176"/>
       <c r="I1" s="176"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="77" t="s">
+      <c r="J1" s="119"/>
+      <c r="K1" s="118" t="s">
         <v>4</v>
       </c>
       <c r="L1" s="176"/>
       <c r="M1" s="176"/>
-      <c r="N1" s="78"/>
-      <c r="O1" s="77" t="s">
+      <c r="N1" s="119"/>
+      <c r="O1" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="77" t="s">
+      <c r="P1" s="119"/>
+      <c r="Q1" s="118" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="78"/>
-      <c r="S1" s="77" t="s">
+      <c r="R1" s="119"/>
+      <c r="S1" s="118" t="s">
         <v>7</v>
       </c>
       <c r="T1" s="178"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="102"/>
-      <c r="B2" s="87"/>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="90"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="84"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="90"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="90"/>
-      <c r="Q2" s="89"/>
-      <c r="R2" s="90"/>
-      <c r="S2" s="89"/>
+      <c r="A2" s="113"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="121"/>
+      <c r="K2" s="120"/>
+      <c r="L2" s="155"/>
+      <c r="M2" s="155"/>
+      <c r="N2" s="121"/>
+      <c r="O2" s="120"/>
+      <c r="P2" s="121"/>
+      <c r="Q2" s="120"/>
+      <c r="R2" s="121"/>
+      <c r="S2" s="120"/>
       <c r="T2" s="183"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="102"/>
-      <c r="B3" s="87"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="92"/>
-      <c r="G3" s="91"/>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="92"/>
-      <c r="K3" s="91"/>
-      <c r="L3" s="87"/>
-      <c r="M3" s="87"/>
-      <c r="N3" s="92"/>
-      <c r="O3" s="91"/>
-      <c r="P3" s="92"/>
-      <c r="Q3" s="91"/>
-      <c r="R3" s="92"/>
-      <c r="S3" s="91"/>
+      <c r="A3" s="113"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="114"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="114"/>
+      <c r="K3" s="122"/>
+      <c r="L3" s="99"/>
+      <c r="M3" s="99"/>
+      <c r="N3" s="114"/>
+      <c r="O3" s="122"/>
+      <c r="P3" s="114"/>
+      <c r="Q3" s="122"/>
+      <c r="R3" s="114"/>
+      <c r="S3" s="122"/>
       <c r="T3" s="184"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="119"/>
-      <c r="B4" s="120"/>
-      <c r="C4" s="120"/>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="122"/>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="122"/>
-      <c r="L4" s="120"/>
-      <c r="M4" s="120"/>
-      <c r="N4" s="121"/>
-      <c r="O4" s="122"/>
-      <c r="P4" s="121"/>
-      <c r="Q4" s="122"/>
-      <c r="R4" s="121"/>
-      <c r="S4" s="122"/>
+      <c r="A4" s="115"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="123"/>
+      <c r="L4" s="116"/>
+      <c r="M4" s="116"/>
+      <c r="N4" s="117"/>
+      <c r="O4" s="123"/>
+      <c r="P4" s="117"/>
+      <c r="Q4" s="123"/>
+      <c r="R4" s="117"/>
+      <c r="S4" s="123"/>
       <c r="T4" s="185"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
@@ -9736,7 +9732,7 @@
       <c r="C5" s="176"/>
       <c r="D5" s="176"/>
       <c r="E5" s="176"/>
-      <c r="F5" s="78"/>
+      <c r="F5" s="119"/>
       <c r="G5" s="177" t="s">
         <v>32</v>
       </c>
@@ -9758,52 +9754,52 @@
       <c r="A6" s="179" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="53" t="s">
+      <c r="B6" s="96"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="96"/>
+      <c r="E6" s="96"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="126" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="54"/>
-      <c r="M6" s="54"/>
-      <c r="N6" s="54"/>
-      <c r="O6" s="54"/>
-      <c r="P6" s="54"/>
-      <c r="Q6" s="54"/>
-      <c r="R6" s="54"/>
-      <c r="S6" s="54"/>
+      <c r="H6" s="96"/>
+      <c r="I6" s="96"/>
+      <c r="J6" s="96"/>
+      <c r="K6" s="96"/>
+      <c r="L6" s="96"/>
+      <c r="M6" s="96"/>
+      <c r="N6" s="96"/>
+      <c r="O6" s="96"/>
+      <c r="P6" s="96"/>
+      <c r="Q6" s="96"/>
+      <c r="R6" s="96"/>
+      <c r="S6" s="96"/>
       <c r="T6" s="180"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
       <c r="A7" s="179" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="53" t="s">
+      <c r="B7" s="96"/>
+      <c r="C7" s="96"/>
+      <c r="D7" s="96"/>
+      <c r="E7" s="96"/>
+      <c r="F7" s="97"/>
+      <c r="G7" s="126" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="54"/>
-      <c r="K7" s="54"/>
-      <c r="L7" s="54"/>
-      <c r="M7" s="54"/>
-      <c r="N7" s="54"/>
-      <c r="O7" s="54"/>
-      <c r="P7" s="54"/>
-      <c r="Q7" s="54"/>
-      <c r="R7" s="54"/>
-      <c r="S7" s="54"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="96"/>
+      <c r="J7" s="96"/>
+      <c r="K7" s="96"/>
+      <c r="L7" s="96"/>
+      <c r="M7" s="96"/>
+      <c r="N7" s="96"/>
+      <c r="O7" s="96"/>
+      <c r="P7" s="96"/>
+      <c r="Q7" s="96"/>
+      <c r="R7" s="96"/>
+      <c r="S7" s="96"/>
       <c r="T7" s="180"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
@@ -10006,34 +10002,34 @@
       <c r="A15" s="179" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="69"/>
+      <c r="B15" s="97"/>
       <c r="C15" s="182" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="69"/>
-      <c r="E15" s="67" t="s">
+      <c r="D15" s="97"/>
+      <c r="E15" s="139" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="69"/>
-      <c r="G15" s="67" t="s">
+      <c r="F15" s="97"/>
+      <c r="G15" s="139" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="54"/>
-      <c r="I15" s="69"/>
-      <c r="J15" s="67" t="s">
+      <c r="H15" s="96"/>
+      <c r="I15" s="97"/>
+      <c r="J15" s="139" t="s">
         <v>45</v>
       </c>
-      <c r="K15" s="69"/>
-      <c r="L15" s="67" t="s">
+      <c r="K15" s="97"/>
+      <c r="L15" s="139" t="s">
         <v>46</v>
       </c>
-      <c r="M15" s="54"/>
-      <c r="N15" s="69"/>
-      <c r="O15" s="67" t="s">
+      <c r="M15" s="96"/>
+      <c r="N15" s="97"/>
+      <c r="O15" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="P15" s="54"/>
-      <c r="Q15" s="69"/>
+      <c r="P15" s="96"/>
+      <c r="Q15" s="97"/>
       <c r="R15" s="13" t="s">
         <v>48</v>
       </c>
@@ -10048,34 +10044,34 @@
       <c r="A16" s="167">
         <v>1</v>
       </c>
-      <c r="B16" s="69"/>
+      <c r="B16" s="97"/>
       <c r="C16" s="168" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="69"/>
+      <c r="D16" s="97"/>
       <c r="E16" s="168" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="69"/>
+      <c r="F16" s="97"/>
       <c r="G16" s="181" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="54"/>
-      <c r="I16" s="69"/>
+      <c r="H16" s="96"/>
+      <c r="I16" s="97"/>
       <c r="J16" s="181" t="s">
         <v>54</v>
       </c>
-      <c r="K16" s="69"/>
+      <c r="K16" s="97"/>
       <c r="L16" s="172" t="s">
         <v>55</v>
       </c>
-      <c r="M16" s="54"/>
-      <c r="N16" s="69"/>
+      <c r="M16" s="96"/>
+      <c r="N16" s="97"/>
       <c r="O16" s="172" t="s">
         <v>56</v>
       </c>
-      <c r="P16" s="54"/>
-      <c r="Q16" s="69"/>
+      <c r="P16" s="96"/>
+      <c r="Q16" s="97"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
       <c r="T16" s="29"/>
@@ -10090,34 +10086,34 @@
       <c r="A17" s="167">
         <v>2</v>
       </c>
-      <c r="B17" s="69"/>
+      <c r="B17" s="97"/>
       <c r="C17" s="168" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="69"/>
+      <c r="D17" s="97"/>
       <c r="E17" s="168" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="69"/>
+      <c r="F17" s="97"/>
       <c r="G17" s="181" t="s">
         <v>59</v>
       </c>
-      <c r="H17" s="54"/>
-      <c r="I17" s="69"/>
+      <c r="H17" s="96"/>
+      <c r="I17" s="97"/>
       <c r="J17" s="181" t="s">
         <v>60</v>
       </c>
-      <c r="K17" s="69"/>
+      <c r="K17" s="97"/>
       <c r="L17" s="172" t="s">
         <v>61</v>
       </c>
-      <c r="M17" s="54"/>
-      <c r="N17" s="69"/>
+      <c r="M17" s="96"/>
+      <c r="N17" s="97"/>
       <c r="O17" s="172" t="s">
         <v>62</v>
       </c>
-      <c r="P17" s="54"/>
-      <c r="Q17" s="69"/>
+      <c r="P17" s="96"/>
+      <c r="Q17" s="97"/>
       <c r="R17" s="28"/>
       <c r="S17" s="28"/>
       <c r="T17" s="29"/>
@@ -10130,22 +10126,22 @@
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
       <c r="A18" s="167"/>
-      <c r="B18" s="69"/>
+      <c r="B18" s="97"/>
       <c r="C18" s="168"/>
-      <c r="D18" s="69"/>
+      <c r="D18" s="97"/>
       <c r="E18" s="168"/>
-      <c r="F18" s="69"/>
+      <c r="F18" s="97"/>
       <c r="G18" s="181"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="69"/>
+      <c r="H18" s="96"/>
+      <c r="I18" s="97"/>
       <c r="J18" s="181"/>
-      <c r="K18" s="69"/>
+      <c r="K18" s="97"/>
       <c r="L18" s="172"/>
-      <c r="M18" s="54"/>
-      <c r="N18" s="69"/>
+      <c r="M18" s="96"/>
+      <c r="N18" s="97"/>
       <c r="O18" s="172"/>
-      <c r="P18" s="54"/>
-      <c r="Q18" s="69"/>
+      <c r="P18" s="96"/>
+      <c r="Q18" s="97"/>
       <c r="R18" s="28"/>
       <c r="S18" s="28"/>
       <c r="T18" s="29"/>
@@ -10158,22 +10154,22 @@
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
       <c r="A19" s="167"/>
-      <c r="B19" s="69"/>
+      <c r="B19" s="97"/>
       <c r="C19" s="168"/>
-      <c r="D19" s="69"/>
+      <c r="D19" s="97"/>
       <c r="E19" s="168"/>
-      <c r="F19" s="69"/>
+      <c r="F19" s="97"/>
       <c r="G19" s="181"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="69"/>
+      <c r="H19" s="96"/>
+      <c r="I19" s="97"/>
       <c r="J19" s="181"/>
-      <c r="K19" s="69"/>
+      <c r="K19" s="97"/>
       <c r="L19" s="172"/>
-      <c r="M19" s="54"/>
-      <c r="N19" s="69"/>
+      <c r="M19" s="96"/>
+      <c r="N19" s="97"/>
       <c r="O19" s="172"/>
-      <c r="P19" s="54"/>
-      <c r="Q19" s="69"/>
+      <c r="P19" s="96"/>
+      <c r="Q19" s="97"/>
       <c r="R19" s="28"/>
       <c r="S19" s="28"/>
       <c r="T19" s="29"/>
@@ -10186,22 +10182,22 @@
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
       <c r="A20" s="167"/>
-      <c r="B20" s="69"/>
+      <c r="B20" s="97"/>
       <c r="C20" s="168"/>
-      <c r="D20" s="69"/>
+      <c r="D20" s="97"/>
       <c r="E20" s="168"/>
-      <c r="F20" s="69"/>
+      <c r="F20" s="97"/>
       <c r="G20" s="181"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="69"/>
+      <c r="H20" s="96"/>
+      <c r="I20" s="97"/>
       <c r="J20" s="181"/>
-      <c r="K20" s="69"/>
+      <c r="K20" s="97"/>
       <c r="L20" s="172"/>
-      <c r="M20" s="54"/>
-      <c r="N20" s="69"/>
+      <c r="M20" s="96"/>
+      <c r="N20" s="97"/>
       <c r="O20" s="172"/>
-      <c r="P20" s="54"/>
-      <c r="Q20" s="69"/>
+      <c r="P20" s="96"/>
+      <c r="Q20" s="97"/>
       <c r="R20" s="28"/>
       <c r="S20" s="28"/>
       <c r="T20" s="29"/>
@@ -10214,22 +10210,22 @@
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
       <c r="A21" s="167"/>
-      <c r="B21" s="69"/>
+      <c r="B21" s="97"/>
       <c r="C21" s="168"/>
-      <c r="D21" s="69"/>
+      <c r="D21" s="97"/>
       <c r="E21" s="168"/>
-      <c r="F21" s="69"/>
+      <c r="F21" s="97"/>
       <c r="G21" s="181"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="69"/>
+      <c r="H21" s="96"/>
+      <c r="I21" s="97"/>
       <c r="J21" s="181"/>
-      <c r="K21" s="69"/>
+      <c r="K21" s="97"/>
       <c r="L21" s="172"/>
-      <c r="M21" s="54"/>
-      <c r="N21" s="69"/>
+      <c r="M21" s="96"/>
+      <c r="N21" s="97"/>
       <c r="O21" s="172"/>
-      <c r="P21" s="54"/>
-      <c r="Q21" s="69"/>
+      <c r="P21" s="96"/>
+      <c r="Q21" s="97"/>
       <c r="R21" s="28"/>
       <c r="S21" s="28"/>
       <c r="T21" s="29"/>
@@ -10242,22 +10238,22 @@
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
       <c r="A22" s="167"/>
-      <c r="B22" s="69"/>
+      <c r="B22" s="97"/>
       <c r="C22" s="168"/>
-      <c r="D22" s="69"/>
+      <c r="D22" s="97"/>
       <c r="E22" s="168"/>
-      <c r="F22" s="69"/>
+      <c r="F22" s="97"/>
       <c r="G22" s="181"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="69"/>
+      <c r="H22" s="96"/>
+      <c r="I22" s="97"/>
       <c r="J22" s="181"/>
-      <c r="K22" s="69"/>
+      <c r="K22" s="97"/>
       <c r="L22" s="172"/>
-      <c r="M22" s="54"/>
-      <c r="N22" s="69"/>
+      <c r="M22" s="96"/>
+      <c r="N22" s="97"/>
       <c r="O22" s="172"/>
-      <c r="P22" s="54"/>
-      <c r="Q22" s="69"/>
+      <c r="P22" s="96"/>
+      <c r="Q22" s="97"/>
       <c r="R22" s="28"/>
       <c r="S22" s="28"/>
       <c r="T22" s="29"/>
@@ -10270,22 +10266,22 @@
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
       <c r="A23" s="167"/>
-      <c r="B23" s="69"/>
+      <c r="B23" s="97"/>
       <c r="C23" s="168"/>
-      <c r="D23" s="69"/>
+      <c r="D23" s="97"/>
       <c r="E23" s="168"/>
-      <c r="F23" s="69"/>
+      <c r="F23" s="97"/>
       <c r="G23" s="181"/>
-      <c r="H23" s="54"/>
-      <c r="I23" s="69"/>
+      <c r="H23" s="96"/>
+      <c r="I23" s="97"/>
       <c r="J23" s="181"/>
-      <c r="K23" s="69"/>
+      <c r="K23" s="97"/>
       <c r="L23" s="172"/>
-      <c r="M23" s="54"/>
-      <c r="N23" s="69"/>
+      <c r="M23" s="96"/>
+      <c r="N23" s="97"/>
       <c r="O23" s="172"/>
-      <c r="P23" s="54"/>
-      <c r="Q23" s="69"/>
+      <c r="P23" s="96"/>
+      <c r="Q23" s="97"/>
       <c r="R23" s="28"/>
       <c r="S23" s="28"/>
       <c r="T23" s="29"/>
@@ -10298,22 +10294,22 @@
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
       <c r="A24" s="167"/>
-      <c r="B24" s="69"/>
+      <c r="B24" s="97"/>
       <c r="C24" s="168"/>
-      <c r="D24" s="69"/>
+      <c r="D24" s="97"/>
       <c r="E24" s="168"/>
-      <c r="F24" s="69"/>
+      <c r="F24" s="97"/>
       <c r="G24" s="181"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="69"/>
+      <c r="H24" s="96"/>
+      <c r="I24" s="97"/>
       <c r="J24" s="181"/>
-      <c r="K24" s="69"/>
+      <c r="K24" s="97"/>
       <c r="L24" s="172"/>
-      <c r="M24" s="54"/>
-      <c r="N24" s="69"/>
+      <c r="M24" s="96"/>
+      <c r="N24" s="97"/>
       <c r="O24" s="172"/>
-      <c r="P24" s="54"/>
-      <c r="Q24" s="69"/>
+      <c r="P24" s="96"/>
+      <c r="Q24" s="97"/>
       <c r="R24" s="28"/>
       <c r="S24" s="28"/>
       <c r="T24" s="29"/>
@@ -10326,22 +10322,22 @@
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
       <c r="A25" s="167"/>
-      <c r="B25" s="69"/>
+      <c r="B25" s="97"/>
       <c r="C25" s="168"/>
-      <c r="D25" s="69"/>
+      <c r="D25" s="97"/>
       <c r="E25" s="168"/>
-      <c r="F25" s="69"/>
+      <c r="F25" s="97"/>
       <c r="G25" s="181"/>
-      <c r="H25" s="54"/>
-      <c r="I25" s="69"/>
+      <c r="H25" s="96"/>
+      <c r="I25" s="97"/>
       <c r="J25" s="181"/>
-      <c r="K25" s="69"/>
+      <c r="K25" s="97"/>
       <c r="L25" s="172"/>
-      <c r="M25" s="54"/>
-      <c r="N25" s="69"/>
+      <c r="M25" s="96"/>
+      <c r="N25" s="97"/>
       <c r="O25" s="172"/>
-      <c r="P25" s="54"/>
-      <c r="Q25" s="69"/>
+      <c r="P25" s="96"/>
+      <c r="Q25" s="97"/>
       <c r="R25" s="28"/>
       <c r="S25" s="28"/>
       <c r="T25" s="29"/>
@@ -10354,22 +10350,22 @@
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
       <c r="A26" s="167"/>
-      <c r="B26" s="69"/>
+      <c r="B26" s="97"/>
       <c r="C26" s="168"/>
-      <c r="D26" s="69"/>
+      <c r="D26" s="97"/>
       <c r="E26" s="168"/>
-      <c r="F26" s="69"/>
+      <c r="F26" s="97"/>
       <c r="G26" s="181"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="69"/>
+      <c r="H26" s="96"/>
+      <c r="I26" s="97"/>
       <c r="J26" s="181"/>
-      <c r="K26" s="69"/>
+      <c r="K26" s="97"/>
       <c r="L26" s="172"/>
-      <c r="M26" s="54"/>
-      <c r="N26" s="69"/>
+      <c r="M26" s="96"/>
+      <c r="N26" s="97"/>
       <c r="O26" s="172"/>
-      <c r="P26" s="54"/>
-      <c r="Q26" s="69"/>
+      <c r="P26" s="96"/>
+      <c r="Q26" s="97"/>
       <c r="R26" s="28"/>
       <c r="S26" s="28"/>
       <c r="T26" s="29"/>
@@ -10382,22 +10378,22 @@
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
       <c r="A27" s="167"/>
-      <c r="B27" s="69"/>
+      <c r="B27" s="97"/>
       <c r="C27" s="168"/>
-      <c r="D27" s="69"/>
+      <c r="D27" s="97"/>
       <c r="E27" s="168"/>
-      <c r="F27" s="69"/>
+      <c r="F27" s="97"/>
       <c r="G27" s="181"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="69"/>
+      <c r="H27" s="96"/>
+      <c r="I27" s="97"/>
       <c r="J27" s="181"/>
-      <c r="K27" s="69"/>
+      <c r="K27" s="97"/>
       <c r="L27" s="172"/>
-      <c r="M27" s="54"/>
-      <c r="N27" s="69"/>
+      <c r="M27" s="96"/>
+      <c r="N27" s="97"/>
       <c r="O27" s="172"/>
-      <c r="P27" s="54"/>
-      <c r="Q27" s="69"/>
+      <c r="P27" s="96"/>
+      <c r="Q27" s="97"/>
       <c r="R27" s="28"/>
       <c r="S27" s="28"/>
       <c r="T27" s="29"/>
@@ -10410,22 +10406,22 @@
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
       <c r="A28" s="167"/>
-      <c r="B28" s="69"/>
+      <c r="B28" s="97"/>
       <c r="C28" s="168"/>
-      <c r="D28" s="69"/>
+      <c r="D28" s="97"/>
       <c r="E28" s="168"/>
-      <c r="F28" s="69"/>
+      <c r="F28" s="97"/>
       <c r="G28" s="181"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="69"/>
+      <c r="H28" s="96"/>
+      <c r="I28" s="97"/>
       <c r="J28" s="181"/>
-      <c r="K28" s="69"/>
+      <c r="K28" s="97"/>
       <c r="L28" s="172"/>
-      <c r="M28" s="54"/>
-      <c r="N28" s="69"/>
+      <c r="M28" s="96"/>
+      <c r="N28" s="97"/>
       <c r="O28" s="172"/>
-      <c r="P28" s="54"/>
-      <c r="Q28" s="69"/>
+      <c r="P28" s="96"/>
+      <c r="Q28" s="97"/>
       <c r="R28" s="28"/>
       <c r="S28" s="28"/>
       <c r="T28" s="29"/>
@@ -10438,22 +10434,22 @@
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
       <c r="A29" s="167"/>
-      <c r="B29" s="69"/>
+      <c r="B29" s="97"/>
       <c r="C29" s="168"/>
-      <c r="D29" s="69"/>
+      <c r="D29" s="97"/>
       <c r="E29" s="168"/>
-      <c r="F29" s="69"/>
+      <c r="F29" s="97"/>
       <c r="G29" s="181"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="69"/>
+      <c r="H29" s="96"/>
+      <c r="I29" s="97"/>
       <c r="J29" s="181"/>
-      <c r="K29" s="69"/>
+      <c r="K29" s="97"/>
       <c r="L29" s="172"/>
-      <c r="M29" s="54"/>
-      <c r="N29" s="69"/>
+      <c r="M29" s="96"/>
+      <c r="N29" s="97"/>
       <c r="O29" s="172"/>
-      <c r="P29" s="54"/>
-      <c r="Q29" s="69"/>
+      <c r="P29" s="96"/>
+      <c r="Q29" s="97"/>
       <c r="R29" s="28"/>
       <c r="S29" s="28"/>
       <c r="T29" s="29"/>
@@ -10466,22 +10462,22 @@
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
       <c r="A30" s="167"/>
-      <c r="B30" s="69"/>
+      <c r="B30" s="97"/>
       <c r="C30" s="168"/>
-      <c r="D30" s="69"/>
+      <c r="D30" s="97"/>
       <c r="E30" s="168"/>
-      <c r="F30" s="69"/>
+      <c r="F30" s="97"/>
       <c r="G30" s="181"/>
-      <c r="H30" s="54"/>
-      <c r="I30" s="69"/>
+      <c r="H30" s="96"/>
+      <c r="I30" s="97"/>
       <c r="J30" s="181"/>
-      <c r="K30" s="69"/>
+      <c r="K30" s="97"/>
       <c r="L30" s="172"/>
-      <c r="M30" s="54"/>
-      <c r="N30" s="69"/>
+      <c r="M30" s="96"/>
+      <c r="N30" s="97"/>
       <c r="O30" s="172"/>
-      <c r="P30" s="54"/>
-      <c r="Q30" s="69"/>
+      <c r="P30" s="96"/>
+      <c r="Q30" s="97"/>
       <c r="R30" s="28"/>
       <c r="S30" s="28"/>
       <c r="T30" s="29"/>

--- a/プロジェクト型演習_成果物_TasBo_コメント投稿.xlsx
+++ b/プロジェクト型演習_成果物_TasBo_コメント投稿.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER111\Desktop\TasBoドキュメント\コメント投稿\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4C243A-0BDC-4E51-A6E2-62430791A782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8147331D-5261-4150-82FB-7025CBC65F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -414,18 +414,19 @@
     <phoneticPr fontId="9"/>
   </si>
   <si>
-    <t>A1. コメントが未入力の場合（基本フロー6から分岐）
+    <t>A1. コメントが未入力の場合（基本フロー7から分岐）
 a. システムはコメントが未入力であることを検出する。
 b. システムはコメント投稿フォーム画面に「コメントを入力してください。」とエラーメッセージを表示する。
 c. システムはコメント投稿フォーム画面を再表示する。
-A2. コメントが文字数上限を超えている場合（基本フロー6から分岐）
+A2. コメントが文字数上限を超えている場合（基本フロー7から分岐）
 a. システムはコメントが100文字を超えていることを検出する。
 b. システムはコメント投稿フォーム画面に「コメントは100文字以内で入力してください。」とエラーメッセージを表示する。
 c. システムはコメント投稿フォーム画面を再表示する。
-A3. コメント登録前または登録中に対象タスクが削除されていた場合（基本フロー3または6から分岐）
+A3. コメント登録前または登録中に対象タスクが削除されていた場合（基本フロー6から分岐）
 a. システムは対象タスクが存在しないことを検出する。
 b. システムは「対象のタスクは既に削除されています。」とエラーメッセージを表示する。
-c. システムはコメント投稿フォーム画面を再表示する。</t>
+c. システムはタスク一覧画面を表示する。
+d. ユースケースを終了する。</t>
     <phoneticPr fontId="9"/>
   </si>
 </sst>
@@ -1694,6 +1695,54 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1727,21 +1776,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1787,39 +1821,6 @@
     <xf numFmtId="56" fontId="6" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1913,18 +1914,93 @@
     <xf numFmtId="14" fontId="6" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1937,9 +2013,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1952,12 +2025,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1970,70 +2037,52 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2042,62 +2091,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -5374,19 +5375,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="78" t="s">
+      <c r="B1" s="81"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="61"/>
-      <c r="F1" s="78" t="s">
+      <c r="E1" s="77"/>
+      <c r="F1" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="61"/>
+      <c r="G1" s="77"/>
       <c r="H1" s="44" t="s">
         <v>5</v>
       </c>
@@ -5398,194 +5399,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="79" t="s">
+      <c r="A2" s="83"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="90" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="80"/>
-      <c r="F2" s="79" t="s">
+      <c r="E2" s="91"/>
+      <c r="F2" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="80"/>
-      <c r="H2" s="83">
+      <c r="G2" s="91"/>
+      <c r="H2" s="94">
         <v>46195</v>
       </c>
-      <c r="I2" s="53" t="s">
+      <c r="I2" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="56"/>
+      <c r="J2" s="72"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="72"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="57"/>
+      <c r="A3" s="83"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="70"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="73"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="75"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="58"/>
+      <c r="A4" s="86"/>
+      <c r="B4" s="87"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="74"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="59" t="s">
+      <c r="A5" s="75" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="62" t="s">
+      <c r="B5" s="76"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="78" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="63"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="79"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="65"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="67" t="s">
+      <c r="B6" s="54"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="68"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="57"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="65"/>
-      <c r="C7" s="66"/>
-      <c r="D7" s="67" t="s">
+      <c r="B7" s="54"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="65"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
-      <c r="I7" s="65"/>
-      <c r="J7" s="68"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="57"/>
     </row>
     <row r="8" spans="1:10" ht="56.25" customHeight="1">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="65"/>
-      <c r="C8" s="66"/>
-      <c r="D8" s="84" t="s">
+      <c r="B8" s="54"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="65"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="65"/>
-      <c r="H8" s="65"/>
-      <c r="I8" s="65"/>
-      <c r="J8" s="68"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="57"/>
     </row>
     <row r="9" spans="1:10" ht="147.75" customHeight="1">
-      <c r="A9" s="91" t="s">
+      <c r="A9" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="94" t="s">
+      <c r="B9" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="66"/>
-      <c r="D9" s="84" t="s">
+      <c r="C9" s="55"/>
+      <c r="D9" s="56" t="s">
         <v>93</v>
       </c>
-      <c r="E9" s="65"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="65"/>
-      <c r="I9" s="65"/>
-      <c r="J9" s="68"/>
-    </row>
-    <row r="10" spans="1:10" ht="193.5" customHeight="1">
-      <c r="A10" s="92"/>
-      <c r="B10" s="94" t="s">
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="57"/>
+    </row>
+    <row r="10" spans="1:10" ht="228" customHeight="1">
+      <c r="A10" s="66"/>
+      <c r="B10" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="66"/>
-      <c r="D10" s="84" t="s">
+      <c r="C10" s="55"/>
+      <c r="D10" s="56" t="s">
         <v>95</v>
       </c>
-      <c r="E10" s="65"/>
-      <c r="F10" s="65"/>
-      <c r="G10" s="65"/>
-      <c r="H10" s="65"/>
-      <c r="I10" s="65"/>
-      <c r="J10" s="68"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="57"/>
     </row>
     <row r="11" spans="1:10" ht="102.75" customHeight="1">
-      <c r="A11" s="93"/>
-      <c r="B11" s="94" t="s">
+      <c r="A11" s="67"/>
+      <c r="B11" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="66"/>
-      <c r="D11" s="84" t="s">
+      <c r="C11" s="55"/>
+      <c r="D11" s="56" t="s">
         <v>84</v>
       </c>
-      <c r="E11" s="65"/>
-      <c r="F11" s="65"/>
-      <c r="G11" s="65"/>
-      <c r="H11" s="65"/>
-      <c r="I11" s="65"/>
-      <c r="J11" s="68"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="57"/>
     </row>
     <row r="12" spans="1:10" ht="46.5" customHeight="1">
-      <c r="A12" s="64" t="s">
+      <c r="A12" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="65"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="84" t="s">
+      <c r="B12" s="54"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="56" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="65"/>
-      <c r="F12" s="65"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="65"/>
-      <c r="I12" s="65"/>
-      <c r="J12" s="68"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="57"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="85" t="s">
+      <c r="A13" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="86"/>
-      <c r="C13" s="87"/>
-      <c r="D13" s="88" t="s">
+      <c r="B13" s="59"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="61" t="s">
         <v>83</v>
       </c>
-      <c r="E13" s="89"/>
-      <c r="F13" s="89"/>
-      <c r="G13" s="89"/>
-      <c r="H13" s="89"/>
-      <c r="I13" s="89"/>
-      <c r="J13" s="90"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="63"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -6576,6 +6577,18 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -6591,18 +6604,6 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -6625,16 +6626,16 @@
       <c r="A1" s="124" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="78" t="s">
+      <c r="B1" s="81"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="61"/>
-      <c r="F1" s="78" t="s">
+      <c r="E1" s="77"/>
+      <c r="F1" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="61"/>
+      <c r="G1" s="77"/>
       <c r="H1" s="45" t="s">
         <v>5</v>
       </c>
@@ -6646,48 +6647,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="79" t="s">
+      <c r="A2" s="83"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="90" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="80"/>
-      <c r="F2" s="79" t="s">
+      <c r="E2" s="91"/>
+      <c r="F2" s="90" t="s">
         <v>74</v>
       </c>
-      <c r="G2" s="80"/>
+      <c r="G2" s="91"/>
       <c r="H2" s="125">
         <v>46196</v>
       </c>
-      <c r="I2" s="53" t="s">
+      <c r="I2" s="69" t="s">
         <v>73</v>
       </c>
-      <c r="J2" s="56"/>
+      <c r="J2" s="72"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="72"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="57"/>
+      <c r="A3" s="83"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="70"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="73"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="75"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="58"/>
+      <c r="A4" s="86"/>
+      <c r="B4" s="87"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="74"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="42"/>
@@ -8171,7 +8172,7 @@
         <v>66</v>
       </c>
       <c r="G2" s="121"/>
-      <c r="H2" s="160">
+      <c r="H2" s="135">
         <v>46196</v>
       </c>
       <c r="I2" s="104" t="s">
@@ -8204,23 +8205,23 @@
       <c r="J4" s="108"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="147" t="s">
+      <c r="A5" s="136" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="148"/>
-      <c r="C5" s="149"/>
-      <c r="D5" s="152" t="s">
+      <c r="B5" s="137"/>
+      <c r="C5" s="138"/>
+      <c r="D5" s="143" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="148"/>
-      <c r="F5" s="148"/>
-      <c r="G5" s="148"/>
-      <c r="H5" s="148"/>
-      <c r="I5" s="148"/>
-      <c r="J5" s="153"/>
+      <c r="E5" s="137"/>
+      <c r="F5" s="137"/>
+      <c r="G5" s="137"/>
+      <c r="H5" s="137"/>
+      <c r="I5" s="137"/>
+      <c r="J5" s="144"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="134" t="s">
+      <c r="A6" s="141" t="s">
         <v>21</v>
       </c>
       <c r="B6" s="96"/>
@@ -8231,22 +8232,22 @@
       <c r="G6" s="96"/>
       <c r="H6" s="96"/>
       <c r="I6" s="96"/>
-      <c r="J6" s="127"/>
+      <c r="J6" s="145"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="154"/>
-      <c r="B7" s="155"/>
-      <c r="C7" s="155"/>
-      <c r="D7" s="155"/>
-      <c r="E7" s="155"/>
-      <c r="F7" s="155"/>
-      <c r="G7" s="155"/>
-      <c r="H7" s="155"/>
-      <c r="I7" s="155"/>
-      <c r="J7" s="156"/>
+      <c r="A7" s="146"/>
+      <c r="B7" s="147"/>
+      <c r="C7" s="147"/>
+      <c r="D7" s="147"/>
+      <c r="E7" s="147"/>
+      <c r="F7" s="147"/>
+      <c r="G7" s="147"/>
+      <c r="H7" s="147"/>
+      <c r="I7" s="147"/>
+      <c r="J7" s="148"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="157"/>
+      <c r="A8" s="149"/>
       <c r="B8" s="99"/>
       <c r="C8" s="99"/>
       <c r="D8" s="99"/>
@@ -8255,10 +8256,10 @@
       <c r="G8" s="99"/>
       <c r="H8" s="99"/>
       <c r="I8" s="99"/>
-      <c r="J8" s="158"/>
+      <c r="J8" s="150"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="157"/>
+      <c r="A9" s="149"/>
       <c r="B9" s="99"/>
       <c r="C9" s="99"/>
       <c r="D9" s="99"/>
@@ -8267,10 +8268,10 @@
       <c r="G9" s="99"/>
       <c r="H9" s="99"/>
       <c r="I9" s="99"/>
-      <c r="J9" s="158"/>
+      <c r="J9" s="150"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="157"/>
+      <c r="A10" s="149"/>
       <c r="B10" s="99"/>
       <c r="C10" s="99"/>
       <c r="D10" s="99"/>
@@ -8279,10 +8280,10 @@
       <c r="G10" s="99"/>
       <c r="H10" s="99"/>
       <c r="I10" s="99"/>
-      <c r="J10" s="158"/>
+      <c r="J10" s="150"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="157"/>
+      <c r="A11" s="149"/>
       <c r="B11" s="99"/>
       <c r="C11" s="99"/>
       <c r="D11" s="99"/>
@@ -8291,10 +8292,10 @@
       <c r="G11" s="99"/>
       <c r="H11" s="99"/>
       <c r="I11" s="99"/>
-      <c r="J11" s="158"/>
+      <c r="J11" s="150"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="157"/>
+      <c r="A12" s="149"/>
       <c r="B12" s="99"/>
       <c r="C12" s="99"/>
       <c r="D12" s="99"/>
@@ -8303,10 +8304,10 @@
       <c r="G12" s="99"/>
       <c r="H12" s="99"/>
       <c r="I12" s="99"/>
-      <c r="J12" s="158"/>
+      <c r="J12" s="150"/>
     </row>
     <row r="13" spans="1:10" ht="93" customHeight="1">
-      <c r="A13" s="157"/>
+      <c r="A13" s="149"/>
       <c r="B13" s="99"/>
       <c r="C13" s="99"/>
       <c r="D13" s="99"/>
@@ -8315,10 +8316,10 @@
       <c r="G13" s="99"/>
       <c r="H13" s="99"/>
       <c r="I13" s="99"/>
-      <c r="J13" s="158"/>
+      <c r="J13" s="150"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="134" t="s">
+      <c r="A14" s="141" t="s">
         <v>22</v>
       </c>
       <c r="B14" s="96"/>
@@ -8329,15 +8330,15 @@
       <c r="G14" s="96"/>
       <c r="H14" s="96"/>
       <c r="I14" s="96"/>
-      <c r="J14" s="127"/>
+      <c r="J14" s="145"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="134" t="s">
+      <c r="A15" s="141" t="s">
         <v>23</v>
       </c>
       <c r="B15" s="96"/>
       <c r="C15" s="97"/>
-      <c r="D15" s="126" t="s">
+      <c r="D15" s="151" t="s">
         <v>85</v>
       </c>
       <c r="E15" s="96"/>
@@ -8352,7 +8353,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="134" t="s">
+      <c r="A16" s="141" t="s">
         <v>25</v>
       </c>
       <c r="B16" s="96"/>
@@ -8369,14 +8370,14 @@
       <c r="G16" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="139" t="s">
+      <c r="H16" s="152" t="s">
         <v>16</v>
       </c>
       <c r="I16" s="96"/>
-      <c r="J16" s="127"/>
+      <c r="J16" s="145"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="140">
+      <c r="A17" s="142">
         <v>1</v>
       </c>
       <c r="B17" s="96"/>
@@ -8393,14 +8394,14 @@
       <c r="G17" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="H17" s="126" t="s">
+      <c r="H17" s="151" t="s">
         <v>71</v>
       </c>
       <c r="I17" s="96"/>
-      <c r="J17" s="127"/>
+      <c r="J17" s="145"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="140">
+      <c r="A18" s="142">
         <v>2</v>
       </c>
       <c r="B18" s="96"/>
@@ -8417,51 +8418,51 @@
       <c r="G18" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="H18" s="126" t="s">
+      <c r="H18" s="151" t="s">
         <v>69</v>
       </c>
       <c r="I18" s="96"/>
-      <c r="J18" s="127"/>
+      <c r="J18" s="145"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="140"/>
+      <c r="A19" s="142"/>
       <c r="B19" s="96"/>
       <c r="C19" s="97"/>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
       <c r="F19" s="15"/>
       <c r="G19" s="15"/>
-      <c r="H19" s="126"/>
+      <c r="H19" s="151"/>
       <c r="I19" s="96"/>
-      <c r="J19" s="127"/>
+      <c r="J19" s="145"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="134" t="s">
+      <c r="A20" s="141" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="135"/>
-      <c r="C20" s="135"/>
-      <c r="D20" s="135"/>
-      <c r="E20" s="135"/>
-      <c r="F20" s="135"/>
-      <c r="G20" s="135"/>
-      <c r="H20" s="135"/>
-      <c r="I20" s="135"/>
-      <c r="J20" s="136"/>
+      <c r="B20" s="159"/>
+      <c r="C20" s="159"/>
+      <c r="D20" s="159"/>
+      <c r="E20" s="159"/>
+      <c r="F20" s="159"/>
+      <c r="G20" s="159"/>
+      <c r="H20" s="159"/>
+      <c r="I20" s="159"/>
+      <c r="J20" s="160"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="134" t="s">
+      <c r="A21" s="141" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="135"/>
-      <c r="C21" s="141"/>
-      <c r="D21" s="126" t="s">
+      <c r="B21" s="159"/>
+      <c r="C21" s="163"/>
+      <c r="D21" s="151" t="s">
         <v>91</v>
       </c>
-      <c r="E21" s="137"/>
-      <c r="F21" s="137"/>
-      <c r="G21" s="137"/>
-      <c r="H21" s="138"/>
+      <c r="E21" s="161"/>
+      <c r="F21" s="161"/>
+      <c r="G21" s="161"/>
+      <c r="H21" s="162"/>
       <c r="I21" s="13" t="s">
         <v>24</v>
       </c>
@@ -8470,11 +8471,11 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="142" t="s">
+      <c r="A22" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="143"/>
-      <c r="C22" s="144"/>
+      <c r="B22" s="165"/>
+      <c r="C22" s="166"/>
       <c r="D22" s="13" t="s">
         <v>26</v>
       </c>
@@ -8487,18 +8488,18 @@
       <c r="G22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="H22" s="139" t="s">
+      <c r="H22" s="152" t="s">
         <v>16</v>
       </c>
-      <c r="I22" s="135"/>
-      <c r="J22" s="136"/>
+      <c r="I22" s="159"/>
+      <c r="J22" s="160"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="145">
+      <c r="A23" s="126">
         <v>3</v>
       </c>
-      <c r="B23" s="146"/>
-      <c r="C23" s="146"/>
+      <c r="B23" s="127"/>
+      <c r="C23" s="127"/>
       <c r="D23" s="33" t="s">
         <v>92</v>
       </c>
@@ -8511,83 +8512,83 @@
       <c r="G23" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="H23" s="126" t="s">
+      <c r="H23" s="151" t="s">
         <v>69</v>
       </c>
       <c r="I23" s="96"/>
-      <c r="J23" s="127"/>
+      <c r="J23" s="145"/>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="145"/>
-      <c r="B24" s="146"/>
-      <c r="C24" s="146"/>
+      <c r="A24" s="126"/>
+      <c r="B24" s="127"/>
+      <c r="C24" s="127"/>
       <c r="D24" s="33"/>
       <c r="E24" s="33"/>
       <c r="F24" s="34"/>
       <c r="G24" s="34"/>
-      <c r="H24" s="126"/>
+      <c r="H24" s="151"/>
       <c r="I24" s="96"/>
-      <c r="J24" s="127"/>
+      <c r="J24" s="145"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="150"/>
-      <c r="B25" s="151"/>
-      <c r="C25" s="151"/>
+      <c r="A25" s="139"/>
+      <c r="B25" s="140"/>
+      <c r="C25" s="140"/>
       <c r="D25" s="48"/>
       <c r="E25" s="48"/>
       <c r="F25" s="49"/>
       <c r="G25" s="49"/>
-      <c r="H25" s="159"/>
-      <c r="I25" s="155"/>
-      <c r="J25" s="156"/>
+      <c r="H25" s="153"/>
+      <c r="I25" s="147"/>
+      <c r="J25" s="148"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A26" s="128"/>
+      <c r="A26" s="154"/>
       <c r="B26" s="129"/>
-      <c r="C26" s="130"/>
+      <c r="C26" s="155"/>
       <c r="D26" s="47"/>
       <c r="E26" s="47"/>
       <c r="F26" s="47"/>
       <c r="G26" s="47"/>
-      <c r="H26" s="131"/>
-      <c r="I26" s="132"/>
-      <c r="J26" s="133"/>
+      <c r="H26" s="156"/>
+      <c r="I26" s="157"/>
+      <c r="J26" s="158"/>
     </row>
     <row r="27" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A27" s="145"/>
-      <c r="B27" s="146"/>
-      <c r="C27" s="146"/>
+      <c r="A27" s="126"/>
+      <c r="B27" s="127"/>
+      <c r="C27" s="127"/>
       <c r="D27" s="34"/>
       <c r="E27" s="47"/>
       <c r="F27" s="47"/>
       <c r="G27" s="47"/>
-      <c r="H27" s="131"/>
-      <c r="I27" s="132"/>
-      <c r="J27" s="133"/>
+      <c r="H27" s="156"/>
+      <c r="I27" s="157"/>
+      <c r="J27" s="158"/>
     </row>
     <row r="28" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A28" s="145"/>
-      <c r="B28" s="146"/>
-      <c r="C28" s="146"/>
+      <c r="A28" s="126"/>
+      <c r="B28" s="127"/>
+      <c r="C28" s="127"/>
       <c r="D28" s="33"/>
       <c r="E28" s="33"/>
       <c r="F28" s="33"/>
       <c r="G28" s="33"/>
-      <c r="H28" s="161"/>
+      <c r="H28" s="128"/>
       <c r="I28" s="129"/>
-      <c r="J28" s="162"/>
+      <c r="J28" s="130"/>
     </row>
     <row r="29" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A29" s="163"/>
-      <c r="B29" s="164"/>
-      <c r="C29" s="164"/>
+      <c r="A29" s="131"/>
+      <c r="B29" s="132"/>
+      <c r="C29" s="132"/>
       <c r="D29" s="51"/>
       <c r="E29" s="51"/>
       <c r="F29" s="52"/>
       <c r="G29" s="52"/>
-      <c r="H29" s="165"/>
-      <c r="I29" s="164"/>
-      <c r="J29" s="166"/>
+      <c r="H29" s="133"/>
+      <c r="I29" s="132"/>
+      <c r="J29" s="134"/>
     </row>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9564,16 +9565,22 @@
     <row r="1002" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H24:J24"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -9590,22 +9597,16 @@
     <mergeCell ref="H18:J18"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="H29:J29"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9625,7 +9626,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="186" t="s">
+      <c r="A1" s="176" t="s">
         <v>30</v>
       </c>
       <c r="B1" s="111"/>
@@ -9636,14 +9637,14 @@
       <c r="G1" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="176"/>
-      <c r="I1" s="176"/>
+      <c r="H1" s="177"/>
+      <c r="I1" s="177"/>
       <c r="J1" s="119"/>
       <c r="K1" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="176"/>
-      <c r="M1" s="176"/>
+      <c r="L1" s="177"/>
+      <c r="M1" s="177"/>
       <c r="N1" s="119"/>
       <c r="O1" s="118" t="s">
         <v>5</v>
@@ -9666,19 +9667,19 @@
       <c r="E2" s="99"/>
       <c r="F2" s="114"/>
       <c r="G2" s="120"/>
-      <c r="H2" s="155"/>
-      <c r="I2" s="155"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
       <c r="J2" s="121"/>
       <c r="K2" s="120"/>
-      <c r="L2" s="155"/>
-      <c r="M2" s="155"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
       <c r="N2" s="121"/>
       <c r="O2" s="120"/>
       <c r="P2" s="121"/>
       <c r="Q2" s="120"/>
       <c r="R2" s="121"/>
       <c r="S2" s="120"/>
-      <c r="T2" s="183"/>
+      <c r="T2" s="173"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="113"/>
@@ -9700,7 +9701,7 @@
       <c r="Q3" s="122"/>
       <c r="R3" s="114"/>
       <c r="S3" s="122"/>
-      <c r="T3" s="184"/>
+      <c r="T3" s="174"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="115"/>
@@ -9722,36 +9723,36 @@
       <c r="Q4" s="123"/>
       <c r="R4" s="117"/>
       <c r="S4" s="123"/>
-      <c r="T4" s="185"/>
+      <c r="T4" s="175"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="175" t="s">
+      <c r="A5" s="179" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="176"/>
-      <c r="C5" s="176"/>
-      <c r="D5" s="176"/>
-      <c r="E5" s="176"/>
+      <c r="B5" s="177"/>
+      <c r="C5" s="177"/>
+      <c r="D5" s="177"/>
+      <c r="E5" s="177"/>
       <c r="F5" s="119"/>
-      <c r="G5" s="177" t="s">
+      <c r="G5" s="180" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="176"/>
-      <c r="I5" s="176"/>
-      <c r="J5" s="176"/>
-      <c r="K5" s="176"/>
-      <c r="L5" s="176"/>
-      <c r="M5" s="176"/>
-      <c r="N5" s="176"/>
-      <c r="O5" s="176"/>
-      <c r="P5" s="176"/>
-      <c r="Q5" s="176"/>
-      <c r="R5" s="176"/>
-      <c r="S5" s="176"/>
+      <c r="H5" s="177"/>
+      <c r="I5" s="177"/>
+      <c r="J5" s="177"/>
+      <c r="K5" s="177"/>
+      <c r="L5" s="177"/>
+      <c r="M5" s="177"/>
+      <c r="N5" s="177"/>
+      <c r="O5" s="177"/>
+      <c r="P5" s="177"/>
+      <c r="Q5" s="177"/>
+      <c r="R5" s="177"/>
+      <c r="S5" s="177"/>
       <c r="T5" s="178"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="179" t="s">
+      <c r="A6" s="181" t="s">
         <v>33</v>
       </c>
       <c r="B6" s="96"/>
@@ -9759,7 +9760,7 @@
       <c r="D6" s="96"/>
       <c r="E6" s="96"/>
       <c r="F6" s="97"/>
-      <c r="G6" s="126" t="s">
+      <c r="G6" s="151" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="96"/>
@@ -9774,10 +9775,10 @@
       <c r="Q6" s="96"/>
       <c r="R6" s="96"/>
       <c r="S6" s="96"/>
-      <c r="T6" s="180"/>
+      <c r="T6" s="182"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="179" t="s">
+      <c r="A7" s="181" t="s">
         <v>34</v>
       </c>
       <c r="B7" s="96"/>
@@ -9785,7 +9786,7 @@
       <c r="D7" s="96"/>
       <c r="E7" s="96"/>
       <c r="F7" s="97"/>
-      <c r="G7" s="126" t="s">
+      <c r="G7" s="151" t="s">
         <v>35</v>
       </c>
       <c r="H7" s="96"/>
@@ -9800,7 +9801,7 @@
       <c r="Q7" s="96"/>
       <c r="R7" s="96"/>
       <c r="S7" s="96"/>
-      <c r="T7" s="180"/>
+      <c r="T7" s="182"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -9999,33 +10000,33 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="179" t="s">
+      <c r="A15" s="181" t="s">
         <v>42</v>
       </c>
       <c r="B15" s="97"/>
-      <c r="C15" s="182" t="s">
+      <c r="C15" s="185" t="s">
         <v>36</v>
       </c>
       <c r="D15" s="97"/>
-      <c r="E15" s="139" t="s">
+      <c r="E15" s="152" t="s">
         <v>43</v>
       </c>
       <c r="F15" s="97"/>
-      <c r="G15" s="139" t="s">
+      <c r="G15" s="152" t="s">
         <v>44</v>
       </c>
       <c r="H15" s="96"/>
       <c r="I15" s="97"/>
-      <c r="J15" s="139" t="s">
+      <c r="J15" s="152" t="s">
         <v>45</v>
       </c>
       <c r="K15" s="97"/>
-      <c r="L15" s="139" t="s">
+      <c r="L15" s="152" t="s">
         <v>46</v>
       </c>
       <c r="M15" s="96"/>
       <c r="N15" s="97"/>
-      <c r="O15" s="139" t="s">
+      <c r="O15" s="152" t="s">
         <v>47</v>
       </c>
       <c r="P15" s="96"/>
@@ -10041,33 +10042,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="167">
+      <c r="A16" s="183">
         <v>1</v>
       </c>
       <c r="B16" s="97"/>
-      <c r="C16" s="168" t="s">
+      <c r="C16" s="184" t="s">
         <v>51</v>
       </c>
       <c r="D16" s="97"/>
-      <c r="E16" s="168" t="s">
+      <c r="E16" s="184" t="s">
         <v>52</v>
       </c>
       <c r="F16" s="97"/>
-      <c r="G16" s="181" t="s">
+      <c r="G16" s="167" t="s">
         <v>53</v>
       </c>
       <c r="H16" s="96"/>
       <c r="I16" s="97"/>
-      <c r="J16" s="181" t="s">
+      <c r="J16" s="167" t="s">
         <v>54</v>
       </c>
       <c r="K16" s="97"/>
-      <c r="L16" s="172" t="s">
+      <c r="L16" s="171" t="s">
         <v>55</v>
       </c>
       <c r="M16" s="96"/>
       <c r="N16" s="97"/>
-      <c r="O16" s="172" t="s">
+      <c r="O16" s="171" t="s">
         <v>56</v>
       </c>
       <c r="P16" s="96"/>
@@ -10083,33 +10084,33 @@
       <c r="Z16" s="30"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="167">
+      <c r="A17" s="183">
         <v>2</v>
       </c>
       <c r="B17" s="97"/>
-      <c r="C17" s="168" t="s">
+      <c r="C17" s="184" t="s">
         <v>57</v>
       </c>
       <c r="D17" s="97"/>
-      <c r="E17" s="168" t="s">
+      <c r="E17" s="184" t="s">
         <v>58</v>
       </c>
       <c r="F17" s="97"/>
-      <c r="G17" s="181" t="s">
+      <c r="G17" s="167" t="s">
         <v>59</v>
       </c>
       <c r="H17" s="96"/>
       <c r="I17" s="97"/>
-      <c r="J17" s="181" t="s">
+      <c r="J17" s="167" t="s">
         <v>60</v>
       </c>
       <c r="K17" s="97"/>
-      <c r="L17" s="172" t="s">
+      <c r="L17" s="171" t="s">
         <v>61</v>
       </c>
       <c r="M17" s="96"/>
       <c r="N17" s="97"/>
-      <c r="O17" s="172" t="s">
+      <c r="O17" s="171" t="s">
         <v>62</v>
       </c>
       <c r="P17" s="96"/>
@@ -10125,21 +10126,21 @@
       <c r="Z17" s="30"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="167"/>
+      <c r="A18" s="183"/>
       <c r="B18" s="97"/>
-      <c r="C18" s="168"/>
+      <c r="C18" s="184"/>
       <c r="D18" s="97"/>
-      <c r="E18" s="168"/>
+      <c r="E18" s="184"/>
       <c r="F18" s="97"/>
-      <c r="G18" s="181"/>
+      <c r="G18" s="167"/>
       <c r="H18" s="96"/>
       <c r="I18" s="97"/>
-      <c r="J18" s="181"/>
+      <c r="J18" s="167"/>
       <c r="K18" s="97"/>
-      <c r="L18" s="172"/>
+      <c r="L18" s="171"/>
       <c r="M18" s="96"/>
       <c r="N18" s="97"/>
-      <c r="O18" s="172"/>
+      <c r="O18" s="171"/>
       <c r="P18" s="96"/>
       <c r="Q18" s="97"/>
       <c r="R18" s="28"/>
@@ -10153,21 +10154,21 @@
       <c r="Z18" s="30"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="167"/>
+      <c r="A19" s="183"/>
       <c r="B19" s="97"/>
-      <c r="C19" s="168"/>
+      <c r="C19" s="184"/>
       <c r="D19" s="97"/>
-      <c r="E19" s="168"/>
+      <c r="E19" s="184"/>
       <c r="F19" s="97"/>
-      <c r="G19" s="181"/>
+      <c r="G19" s="167"/>
       <c r="H19" s="96"/>
       <c r="I19" s="97"/>
-      <c r="J19" s="181"/>
+      <c r="J19" s="167"/>
       <c r="K19" s="97"/>
-      <c r="L19" s="172"/>
+      <c r="L19" s="171"/>
       <c r="M19" s="96"/>
       <c r="N19" s="97"/>
-      <c r="O19" s="172"/>
+      <c r="O19" s="171"/>
       <c r="P19" s="96"/>
       <c r="Q19" s="97"/>
       <c r="R19" s="28"/>
@@ -10181,21 +10182,21 @@
       <c r="Z19" s="30"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="167"/>
+      <c r="A20" s="183"/>
       <c r="B20" s="97"/>
-      <c r="C20" s="168"/>
+      <c r="C20" s="184"/>
       <c r="D20" s="97"/>
-      <c r="E20" s="168"/>
+      <c r="E20" s="184"/>
       <c r="F20" s="97"/>
-      <c r="G20" s="181"/>
+      <c r="G20" s="167"/>
       <c r="H20" s="96"/>
       <c r="I20" s="97"/>
-      <c r="J20" s="181"/>
+      <c r="J20" s="167"/>
       <c r="K20" s="97"/>
-      <c r="L20" s="172"/>
+      <c r="L20" s="171"/>
       <c r="M20" s="96"/>
       <c r="N20" s="97"/>
-      <c r="O20" s="172"/>
+      <c r="O20" s="171"/>
       <c r="P20" s="96"/>
       <c r="Q20" s="97"/>
       <c r="R20" s="28"/>
@@ -10209,21 +10210,21 @@
       <c r="Z20" s="30"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="167"/>
+      <c r="A21" s="183"/>
       <c r="B21" s="97"/>
-      <c r="C21" s="168"/>
+      <c r="C21" s="184"/>
       <c r="D21" s="97"/>
-      <c r="E21" s="168"/>
+      <c r="E21" s="184"/>
       <c r="F21" s="97"/>
-      <c r="G21" s="181"/>
+      <c r="G21" s="167"/>
       <c r="H21" s="96"/>
       <c r="I21" s="97"/>
-      <c r="J21" s="181"/>
+      <c r="J21" s="167"/>
       <c r="K21" s="97"/>
-      <c r="L21" s="172"/>
+      <c r="L21" s="171"/>
       <c r="M21" s="96"/>
       <c r="N21" s="97"/>
-      <c r="O21" s="172"/>
+      <c r="O21" s="171"/>
       <c r="P21" s="96"/>
       <c r="Q21" s="97"/>
       <c r="R21" s="28"/>
@@ -10237,21 +10238,21 @@
       <c r="Z21" s="30"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="167"/>
+      <c r="A22" s="183"/>
       <c r="B22" s="97"/>
-      <c r="C22" s="168"/>
+      <c r="C22" s="184"/>
       <c r="D22" s="97"/>
-      <c r="E22" s="168"/>
+      <c r="E22" s="184"/>
       <c r="F22" s="97"/>
-      <c r="G22" s="181"/>
+      <c r="G22" s="167"/>
       <c r="H22" s="96"/>
       <c r="I22" s="97"/>
-      <c r="J22" s="181"/>
+      <c r="J22" s="167"/>
       <c r="K22" s="97"/>
-      <c r="L22" s="172"/>
+      <c r="L22" s="171"/>
       <c r="M22" s="96"/>
       <c r="N22" s="97"/>
-      <c r="O22" s="172"/>
+      <c r="O22" s="171"/>
       <c r="P22" s="96"/>
       <c r="Q22" s="97"/>
       <c r="R22" s="28"/>
@@ -10265,21 +10266,21 @@
       <c r="Z22" s="30"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="167"/>
+      <c r="A23" s="183"/>
       <c r="B23" s="97"/>
-      <c r="C23" s="168"/>
+      <c r="C23" s="184"/>
       <c r="D23" s="97"/>
-      <c r="E23" s="168"/>
+      <c r="E23" s="184"/>
       <c r="F23" s="97"/>
-      <c r="G23" s="181"/>
+      <c r="G23" s="167"/>
       <c r="H23" s="96"/>
       <c r="I23" s="97"/>
-      <c r="J23" s="181"/>
+      <c r="J23" s="167"/>
       <c r="K23" s="97"/>
-      <c r="L23" s="172"/>
+      <c r="L23" s="171"/>
       <c r="M23" s="96"/>
       <c r="N23" s="97"/>
-      <c r="O23" s="172"/>
+      <c r="O23" s="171"/>
       <c r="P23" s="96"/>
       <c r="Q23" s="97"/>
       <c r="R23" s="28"/>
@@ -10293,21 +10294,21 @@
       <c r="Z23" s="30"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="167"/>
+      <c r="A24" s="183"/>
       <c r="B24" s="97"/>
-      <c r="C24" s="168"/>
+      <c r="C24" s="184"/>
       <c r="D24" s="97"/>
-      <c r="E24" s="168"/>
+      <c r="E24" s="184"/>
       <c r="F24" s="97"/>
-      <c r="G24" s="181"/>
+      <c r="G24" s="167"/>
       <c r="H24" s="96"/>
       <c r="I24" s="97"/>
-      <c r="J24" s="181"/>
+      <c r="J24" s="167"/>
       <c r="K24" s="97"/>
-      <c r="L24" s="172"/>
+      <c r="L24" s="171"/>
       <c r="M24" s="96"/>
       <c r="N24" s="97"/>
-      <c r="O24" s="172"/>
+      <c r="O24" s="171"/>
       <c r="P24" s="96"/>
       <c r="Q24" s="97"/>
       <c r="R24" s="28"/>
@@ -10321,21 +10322,21 @@
       <c r="Z24" s="30"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="167"/>
+      <c r="A25" s="183"/>
       <c r="B25" s="97"/>
-      <c r="C25" s="168"/>
+      <c r="C25" s="184"/>
       <c r="D25" s="97"/>
-      <c r="E25" s="168"/>
+      <c r="E25" s="184"/>
       <c r="F25" s="97"/>
-      <c r="G25" s="181"/>
+      <c r="G25" s="167"/>
       <c r="H25" s="96"/>
       <c r="I25" s="97"/>
-      <c r="J25" s="181"/>
+      <c r="J25" s="167"/>
       <c r="K25" s="97"/>
-      <c r="L25" s="172"/>
+      <c r="L25" s="171"/>
       <c r="M25" s="96"/>
       <c r="N25" s="97"/>
-      <c r="O25" s="172"/>
+      <c r="O25" s="171"/>
       <c r="P25" s="96"/>
       <c r="Q25" s="97"/>
       <c r="R25" s="28"/>
@@ -10349,21 +10350,21 @@
       <c r="Z25" s="30"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="167"/>
+      <c r="A26" s="183"/>
       <c r="B26" s="97"/>
-      <c r="C26" s="168"/>
+      <c r="C26" s="184"/>
       <c r="D26" s="97"/>
-      <c r="E26" s="168"/>
+      <c r="E26" s="184"/>
       <c r="F26" s="97"/>
-      <c r="G26" s="181"/>
+      <c r="G26" s="167"/>
       <c r="H26" s="96"/>
       <c r="I26" s="97"/>
-      <c r="J26" s="181"/>
+      <c r="J26" s="167"/>
       <c r="K26" s="97"/>
-      <c r="L26" s="172"/>
+      <c r="L26" s="171"/>
       <c r="M26" s="96"/>
       <c r="N26" s="97"/>
-      <c r="O26" s="172"/>
+      <c r="O26" s="171"/>
       <c r="P26" s="96"/>
       <c r="Q26" s="97"/>
       <c r="R26" s="28"/>
@@ -10377,21 +10378,21 @@
       <c r="Z26" s="30"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="167"/>
+      <c r="A27" s="183"/>
       <c r="B27" s="97"/>
-      <c r="C27" s="168"/>
+      <c r="C27" s="184"/>
       <c r="D27" s="97"/>
-      <c r="E27" s="168"/>
+      <c r="E27" s="184"/>
       <c r="F27" s="97"/>
-      <c r="G27" s="181"/>
+      <c r="G27" s="167"/>
       <c r="H27" s="96"/>
       <c r="I27" s="97"/>
-      <c r="J27" s="181"/>
+      <c r="J27" s="167"/>
       <c r="K27" s="97"/>
-      <c r="L27" s="172"/>
+      <c r="L27" s="171"/>
       <c r="M27" s="96"/>
       <c r="N27" s="97"/>
-      <c r="O27" s="172"/>
+      <c r="O27" s="171"/>
       <c r="P27" s="96"/>
       <c r="Q27" s="97"/>
       <c r="R27" s="28"/>
@@ -10405,21 +10406,21 @@
       <c r="Z27" s="30"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="167"/>
+      <c r="A28" s="183"/>
       <c r="B28" s="97"/>
-      <c r="C28" s="168"/>
+      <c r="C28" s="184"/>
       <c r="D28" s="97"/>
-      <c r="E28" s="168"/>
+      <c r="E28" s="184"/>
       <c r="F28" s="97"/>
-      <c r="G28" s="181"/>
+      <c r="G28" s="167"/>
       <c r="H28" s="96"/>
       <c r="I28" s="97"/>
-      <c r="J28" s="181"/>
+      <c r="J28" s="167"/>
       <c r="K28" s="97"/>
-      <c r="L28" s="172"/>
+      <c r="L28" s="171"/>
       <c r="M28" s="96"/>
       <c r="N28" s="97"/>
-      <c r="O28" s="172"/>
+      <c r="O28" s="171"/>
       <c r="P28" s="96"/>
       <c r="Q28" s="97"/>
       <c r="R28" s="28"/>
@@ -10433,21 +10434,21 @@
       <c r="Z28" s="30"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="167"/>
+      <c r="A29" s="183"/>
       <c r="B29" s="97"/>
-      <c r="C29" s="168"/>
+      <c r="C29" s="184"/>
       <c r="D29" s="97"/>
-      <c r="E29" s="168"/>
+      <c r="E29" s="184"/>
       <c r="F29" s="97"/>
-      <c r="G29" s="181"/>
+      <c r="G29" s="167"/>
       <c r="H29" s="96"/>
       <c r="I29" s="97"/>
-      <c r="J29" s="181"/>
+      <c r="J29" s="167"/>
       <c r="K29" s="97"/>
-      <c r="L29" s="172"/>
+      <c r="L29" s="171"/>
       <c r="M29" s="96"/>
       <c r="N29" s="97"/>
-      <c r="O29" s="172"/>
+      <c r="O29" s="171"/>
       <c r="P29" s="96"/>
       <c r="Q29" s="97"/>
       <c r="R29" s="28"/>
@@ -10461,21 +10462,21 @@
       <c r="Z29" s="30"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="167"/>
+      <c r="A30" s="183"/>
       <c r="B30" s="97"/>
-      <c r="C30" s="168"/>
+      <c r="C30" s="184"/>
       <c r="D30" s="97"/>
-      <c r="E30" s="168"/>
+      <c r="E30" s="184"/>
       <c r="F30" s="97"/>
-      <c r="G30" s="181"/>
+      <c r="G30" s="167"/>
       <c r="H30" s="96"/>
       <c r="I30" s="97"/>
-      <c r="J30" s="181"/>
+      <c r="J30" s="167"/>
       <c r="K30" s="97"/>
-      <c r="L30" s="172"/>
+      <c r="L30" s="171"/>
       <c r="M30" s="96"/>
       <c r="N30" s="97"/>
-      <c r="O30" s="172"/>
+      <c r="O30" s="171"/>
       <c r="P30" s="96"/>
       <c r="Q30" s="97"/>
       <c r="R30" s="28"/>
@@ -10489,22 +10490,22 @@
       <c r="Z30" s="30"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="169"/>
+      <c r="A31" s="186"/>
       <c r="B31" s="170"/>
-      <c r="C31" s="171"/>
+      <c r="C31" s="187"/>
       <c r="D31" s="170"/>
-      <c r="E31" s="171"/>
+      <c r="E31" s="187"/>
       <c r="F31" s="170"/>
-      <c r="G31" s="187"/>
-      <c r="H31" s="174"/>
+      <c r="G31" s="168"/>
+      <c r="H31" s="169"/>
       <c r="I31" s="170"/>
-      <c r="J31" s="187"/>
+      <c r="J31" s="168"/>
       <c r="K31" s="170"/>
-      <c r="L31" s="173"/>
-      <c r="M31" s="174"/>
+      <c r="L31" s="172"/>
+      <c r="M31" s="169"/>
       <c r="N31" s="170"/>
-      <c r="O31" s="173"/>
-      <c r="P31" s="174"/>
+      <c r="O31" s="172"/>
+      <c r="P31" s="169"/>
       <c r="Q31" s="170"/>
       <c r="R31" s="31"/>
       <c r="S31" s="31"/>
@@ -11503,62 +11504,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -11583,62 +11584,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
